--- a/data/source/2026-09-28/BSR_UK_Mite-Vacuum_Top50_2026-09-28.xlsx
+++ b/data/source/2026-09-28/BSR_UK_Mite-Vacuum_Top50_2026-09-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="315">
   <si>
     <t>#</t>
   </si>
@@ -232,172 +232,756 @@
     <t>B0FBH3FKJH</t>
   </si>
   <si>
-    <t>https://www.amazon.co.ukundefined</t>
-  </si>
-  <si>
-    <t>Hoover HMC5 4-in-1 Mattress Vacuum Cleaner, Anti-Allergen [HMC520UV]sHandheld Dust Mite Vacuum Cleaner for beds and sofas -</t>
+    <t>Colour Name: Black</t>
+  </si>
+  <si>
+    <t>Brand: Hoover | Special feature: Compact, UV Light, Washable Filter | Filter type: Washable Filter | Surface recommendation: Upholstery | Power source: Corded Electric</t>
+  </si>
+  <si>
+    <t>Hoover</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/stores/Hoover/page/93924FFB-1D83-4E54-8B26-4C7644C8FC3E?lp_asin=B0FBH3FKJH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
+    <t>Hoover HMC5 4-in-1 Mattress Vacuum Cleaner, Anti-Allergen [HMC520UV]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Powerful 4-in-1 Mattress Cleaner: Tackle hidden allergens with Hoover's advanced 4-in-1 technology: Beat&amp;Roll, Vacuum, UV-C Light, and Drying functions work together to eliminate dust mites, bacteria, and mould from mattresses and soft furnishings.
+Designed for Beds, Sofas &amp; More: This lightweight Hoover for beds (just 2.2kg) is perfect for mattresses, cushions, and sofas. Powerful suction removes embedded dust, pet hair, and allergens in one go.
+Beat&amp;Roll Technology: The motorised roller rotates 4200 times per minute, lifting dust and debris from deep within your mattress without damaging delicate fabrics. Ideal for allergy sufferers who want a deep clean without hassle.
+Smart Dust Sensor with LED Indicator: See your clean in real time. The smart LED turns from red to green when the surface is free from dust mites, dirt, and allergens – giving you confidence in every clean.
+UV-C Light &amp; Hot Air Drying: Kills bacteria and helps prevent mould growth. The UV light activates only on contact with a surface for safe use. 50°C hot air helps dry damp areas, keeping your mattress fresh and hygienic.</t>
   </si>
   <si>
     <t>https://www.amazon.co.uk/dp/B0FBH3FKJH?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/71mCoX81GcL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/41+wqZaBGEL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0FBTNXCD7</t>
+  </si>
+  <si>
+    <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Vacuums:Futon Vacuums</t>
+  </si>
+  <si>
+    <t>Home &amp; Kitchen</t>
+  </si>
+  <si>
+    <t>Futon Vacuums</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>2025-06-03</t>
+  </si>
+  <si>
+    <t>AMZ</t>
+  </si>
+  <si>
+    <t>10天</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>3.23 Kilograms</t>
+  </si>
+  <si>
+    <t>3.23 kg</t>
+  </si>
+  <si>
+    <t>31.1L x 24W x 19.4H centimetres</t>
+  </si>
+  <si>
+    <t>36.1 x 28 x 24.5 cm</t>
+  </si>
+  <si>
+    <t>36.10 x 28.00 x 24.50 cm</t>
+  </si>
+  <si>
+    <t>标准包裹</t>
   </si>
   <si>
     <t>B0DHL35LFT</t>
   </si>
   <si>
-    <t>Jimmy BX7 Pro Max Mattress &amp; Bed Vacuum Cleaner 700W Power 15kPa Suction with UV-C Light 65°C Heat &amp; Graphene Tech, Dust Mite</t>
+    <t>Brand: Jimmy | Special feature: 65°C graphene heating, High Precision Sensors, Negative ions for air purification, Ultrasonic function | Filter type: HEPA grade MIF filter | Surface recommendation: Mattress, Beds, Pillow, Sofa, Carpet, Upholstery | Power source: Corded Electric</t>
+  </si>
+  <si>
+    <t>Jimmy</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/stores/JIMMY-UK/page/F8F01541-3149-48BD-8244-91EE9CFB1B04?lp_asin=B0DHL35LFT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+  </si>
+  <si>
+    <t>Jimmy BX7 Pro Max Mattress &amp; Bed Vacuum Cleaner 700W Power 15kPa Suction with UV-C Light 65°C Heat &amp; Graphene Tech, Dust Mite Sensor, Negative-ion Function for Mattresses Bed Upholstery Deep Cleaning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">700W POWERFUL SUCTION POWER:The Jimmy BX7 PRO MAX is equipped with a 700W motor that provides strong suction power of 16kPa. So you can easily clean mattresses, bedding, short pile carpets, chairs and sofas. It effectively removes dust mites, dust and deep particles and is ideal for households, hotels and allergy sufferers
+Dust Mite Vacuum Cleaner: The built-in mite sensor detects the concentration of mites on your bed and mattress. Thanks to the real-time color change, you can monitor the level of cleaning and thus clean more accurately, saving time
+Hot Air &amp; Graphene Heating - In addition to traditional hot air, this vacuum cleaner has graphene heating technology that emits hot air up to 65°C. Specially designed for mattresses and bedding, it not only effectively removes dust mites, but also keeps bed linen dry, ideal for use in wet or rainy weather
+Anti-dust mite vacuum cleaner with UV-C light: UV-C light emits a wavelength of 253 nm and effectively cleans mites from mattresses, sofas and textile surfaces. The light will automatically turn off when lifted, ensuring safe use
+Negative ion function: the dust mite vacuum cleaner has a negative ion emitter that continuously releases negative ions during use, which neutralize and reduce dust particles, which helps to keep the air fresh
+Combined Brush Roller The combination brush roller is composed of soft rubber bands and soft bristles. With the 245mm wide suction nozzle, it ensures a high-speed, high-frequency strike that allows for a thorough and efficient cleaning</t>
   </si>
   <si>
     <t>https://www.amazon.co.uk/dp/B0DHL35LFT?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/61Vef2rJE5L._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/41H47yZFjXL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>2025-03-04</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>MINTERZ</t>
+  </si>
+  <si>
+    <t>GB</t>
+  </si>
+  <si>
+    <t>LANCASHIRE LA4 5UE GB</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ALIOQETPFAPZL</t>
+  </si>
+  <si>
+    <t>Carbon impact (ClimatePartner Verified)</t>
+  </si>
+  <si>
+    <t>2.7 Kilograms</t>
+  </si>
+  <si>
+    <t>2.70 kg</t>
+  </si>
+  <si>
+    <t>38.5L x 21.5W x 28H centimetres</t>
+  </si>
+  <si>
+    <t>3.8 kg</t>
+  </si>
+  <si>
+    <t>3.80 kg</t>
+  </si>
+  <si>
+    <t>42.2 x 32.9 x 24.9 cm</t>
+  </si>
+  <si>
+    <t>42.20 x 32.90 x 24.90 cm</t>
+  </si>
+  <si>
+    <t>B0FN3GPQZM</t>
+  </si>
+  <si>
+    <t>Colour Name: Grey</t>
+  </si>
+  <si>
+    <t>Brand: Teant | Special feature: HEPA | Filter type: HEPA Filter | Surface recommendation: Carpet | Power source: Corded Electric</t>
+  </si>
+  <si>
+    <t>Teant</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/stores/ForSimpleLife/page/F3CD0189-4A3C-4A17-A156-96A66C79D903?lp_asin=B0FN3GPQZM&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+  </si>
+  <si>
+    <t>Teant Bed Mattress Vacuum, 18 kPa &amp; Green Light Dust Detection, MV-GREY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Powerful 2-Speed Deep Clean - No Debris Survives] Teant mattress vacuum cleaner offers 2 adjustable suction levels up to 18kPa, while the Hyper Helix motor delivers 33,000-RPM powerful tapping to enter mattresses, sofas, and fabrics, lifting dust, dander, and allergens; dual dust cups and HEPA filter capture 99.97% of microparticles (as small as 0.3µm) and separate hair to prevent clogs, keeping suction strong for deeper, more consistent cleaning and a fresher sleep space
+[Green Light Detection, No Dust Hides] Teant dust mite vacuum cleaner uses 555nm green light and lens technology to reveal hidden dust, pet hair, and microparticles on dark mattresses, sofas, and deep fabric crevices, leaving no spots missed; extra-long 5-meter cord reaches every corner of a king-size bed without unplugging, experience simpler, smarter, and more thorough cleaning
+[Multifunction LED Display for Visualized Cleaning] Intelligent LED with dynamic red and blue indicators shows cleaning progress in real time; the mattress vacuum’s large, clear LED display allows you to instantly monitor functions: Tap, Heat, UV-C, Ultrasonic, and Anion (Tip: prolonged red may indicate the dust sensor is covered; wipe with a clean damp cloth)
+[Target Hidden Microparticles, Protect Your Family] 253.7nm UV-C light combined with 40,000Hz ultrasonic technology, Teant mattress vacuum cleaner with uv light penetrates deep into mattress fibers to target and eliminate 99.9% invisible particles; gravity-sensing dual rollers activate UV only after both wheels contact the surface for 2 seconds and shut off when lifted, preventing light leakage and keeping your family safe
+[Your Triple-Threat for a Fresher Home: Heat, Aroma &amp; Anion] Say goodbye to damp beds and odors! Teant bed mattress vacuum cleaner provides 149°F heated airflow to efficiently dry fabrics, enjoy a clean, dry mattress; negative ion technology helps neutralize airborne particles and refresh the air, while aroma tablet removes odors and adds a subtle natural fragrance, perfect for a clean and cozy night’s sleep
+[Dual Defense: Tangle-Free Brush &amp; Overheat Protection] Teant bed vacuum cleaner features an auto-stop roller brush that halts instantly if tangled, protecting the motor and extending lifespan; built-in overheat protection automatically pauses operation after extended use, just power off, let it cool for 2 hours, then resume cleaning with confidence</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/dp/B0FN3GPQZM?psc=1</t>
+  </si>
+  <si>
+    <t>https://images-na.ssl-images-amazon.com/images/I/71zFBwnc9GL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0GT4XL7VP</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2025-11-22</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>郑州市 河南 450000 CN</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3EVTWEH1TBVG5</t>
+  </si>
+  <si>
+    <t>Carbon impact (ClimeCo Certified)</t>
+  </si>
+  <si>
+    <t>1.9 Kilograms</t>
+  </si>
+  <si>
+    <t>1.90 kg</t>
+  </si>
+  <si>
+    <t>36L x 29W x 25H centimetres</t>
+  </si>
+  <si>
+    <t>2.58 kg</t>
+  </si>
+  <si>
+    <t>33.1 x 30.9 x 27.4 cm</t>
+  </si>
+  <si>
+    <t>33.10 x 30.90 x 27.40 cm</t>
+  </si>
+  <si>
+    <t>轻型标准大件</t>
+  </si>
+  <si>
+    <t>B0FPQMRBYZ</t>
+  </si>
+  <si>
+    <t>Brand: KÄRCHER | Special feature: UV-C light technology and mattress cleaning | Filter type: Foam | Surface recommendation: Upholstery | Power source: Corded Electric</t>
+  </si>
+  <si>
+    <t>KÄRCHER</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/stores/K%C3%A4rcherUK/page/F6053778-BFEE-41CB-9B1B-A16ECF7857D7?lp_asin=B0FPQMRBYZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
+    <t>Kärcher Mattress cleaner VCH 4 UVClean, hygienic deep cleaning with UV-C light, knock roller and suction function, power 500 watts, weight: 2.1 kg, removes mites and bacteria, for people with a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hygienic deep cleaning: the VCH 4 UVClean cleans mattresses, pillows, other textile surfaces and frees them from visible and invisible contamination
+3-way technology: the vibrating knock roller dissolves deep seated dirt and mites, which are then thoroughly vacuumed; the UV-C light neutralises 99.9% of all bacteria and mites
+Container system with 2 compartments: cyclone technology ensures that coarse dirt is collected in one and fine dust in the other chamber; this ensures consistently high suction power
+Compact design: the device with the ergonomic handle weighs 2.1 kg and allows for a long and effortless work; after cleaning, it can be stored away to save space
+Contents: Kärcher mattress cleaner VCH 4 UVClean, knock roller, 2 foam filters, 3 engine protection filters</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/dp/B0FPQMRBYZ?psc=1</t>
+  </si>
+  <si>
+    <t>https://images-na.ssl-images-amazon.com/images/I/81MMJHIRoeL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>2025-12-03</t>
+  </si>
+  <si>
+    <t>Daily Discounts Ltd</t>
+  </si>
+  <si>
+    <t>London Greater London E6 5YU GB</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A36NXA8Q9KKCPB</t>
+  </si>
+  <si>
+    <t>2.5 Kilograms</t>
+  </si>
+  <si>
+    <t>2.50 kg</t>
+  </si>
+  <si>
+    <t>30.9L x 24W x 17H centimetres</t>
+  </si>
+  <si>
+    <t>3.2 kg</t>
+  </si>
+  <si>
+    <t>3.20 kg</t>
+  </si>
+  <si>
+    <t>39.1 x 29.4 x 19.3 cm</t>
+  </si>
+  <si>
+    <t>39.10 x 29.40 x 19.30 cm</t>
   </si>
   <si>
     <t>B0DTS8VCFB</t>
   </si>
   <si>
-    <t>HAUSHOF 400W Mattress Vacuum Cleaner with 16 kPa Suction for Bed &amp; SofasUltrasonic Cleaning, UV-C Light &amp; Hot Air &amp; Roller</t>
+    <t>HAUSHOF</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/stores/HAUSHOF/page/127A78F6-40A3-43F5-9B80-D084EFBE3029?lp_asin=B0DTS8VCFB&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
+    <t>HAUSHOF 400W Mattress Vacuum Cleaner with 16 kPa Suction for Bed &amp; Sofa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 kPa Powerful Suction: The handheld dust mite vacuum delivers strong 16 kPa suction, effectively removing mites, dust, and pet hair from fabric surfaces such as beds, mattresses, sofas, cribs, and carpets—helping keep your home clean and comfortable
+3-in-1 Mite Removal Technology: Mattress cleaner machine combines 275 nm UV-C light, 60 °C hot air, and a beating roller brush to deeply penetrate fabrics and effectively eliminate mites and bacteria
+Powerful Ultrasonic Deep Cleaning: Equipped with advanced ultrasonic technology, the mattress vacuum penetrates deep into fibers to break down stubborn dirt, stains, and bacteria—ensuring a thorough, damage-free clean across the entire surface
+Dual Dust Cup with H11 HEPA Filter: This dust mite vacuum features a 500 ml large-capacity dual dust cup and a separated filtration design to effectively prevent clogging and leakage. Equipped with an H11-grade HEPA filter, it captures fine dust particles to maintain consistent suction and enhance cleaning efficiency
+Extra-Long Cord: The 5-meter extra-long power cord provides extended reach, allowing you to clean large spaces such as bedrooms, living rooms, and hallways without constantly switching outlets. This added convenience ensures uninterrupted cleaning and better efficiency</t>
   </si>
   <si>
     <t>https://www.amazon.co.uk/dp/B0DTS8VCFB?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/616ONjp63mL._AC_UL300_SR300,200_.jpg</t>
-  </si>
-  <si>
-    <t>B0FN3GPQZM</t>
-  </si>
-  <si>
-    <t>Teant Bed Mattress Vacuum, 18 kPa &amp; Green Light Dust Detection, MV-GREYs2-Speed Bed Vacuum Cleaner with 253.7nm UV-C &amp; Ultr</t>
-  </si>
-  <si>
-    <t>https://www.amazon.co.uk/dp/B0FN3GPQZM?psc=1</t>
-  </si>
-  <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/71zFBwnc9GL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/41r3fkBQX2L._AC_US200_.jpg</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>2.56 kg</t>
+  </si>
+  <si>
+    <t>25 x 21.5 x 32.5 cm</t>
+  </si>
+  <si>
+    <t>25.00 x 21.50 x 32.50 cm</t>
+  </si>
+  <si>
+    <t>B0DSCSR4MB</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/stores/HAUSHOF/page/127A78F6-40A3-43F5-9B80-D084EFBE3029?lp_asin=B0DSCSR4MB&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+  </si>
+  <si>
+    <t>HAUSHOF 400 W Mattress Vacuum Cleaner with 15 kPa Suction for Bed &amp; Sofa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 kPa Powerful Suction: The handheld dust mite vacuum delivers strong 15 kPa suction, effectively removing mites, dust, and pet hair from fabric surfaces such as beds, mattresses, sofas, cribs, and carpets—helping keep your home clean and comfortable
+Smart Mite Detection &amp; LED Display: Mattress vacuum features a sensitive mite sensor and digital display that indicates mite levels in real time (Low/Medium/High), making cleaning results easy to monitor
+3-in-1 Mite Removal Technology: Mattress cleaner machine combines 275 nm UV-C light, 60 °C hot air, and a beating roller brush to deeply penetrate fabrics and effectively eliminate mites and bacteria
+Dual Dust Cup with H12 HEPA Filter: This dust mite vacuum features a 500 ml large-capacity dual dust cup and a separated filtration design to effectively prevent clogging and leakage. Equipped with an H12-grade HEPA filter, it captures fine dust particles to maintain consistent suction and enhance cleaning efficiency
+Aromatherapy &amp; Extra-Long Cord: Bed cleaner includes aroma pads and an essential oil sponge slot for a fresh scent during cleaning. 5-meter power cord covers large areas like bedrooms and living rooms with ease</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/dp/B0DSCSR4MB?psc=1</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/418QfGErb0L._AC_US200_.jpg</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>2025-06-25</t>
+  </si>
+  <si>
+    <t>1.82 kg</t>
+  </si>
+  <si>
+    <t>29 x 27 x 18.6 cm</t>
+  </si>
+  <si>
+    <t>29.00 x 27.00 x 18.60 cm</t>
   </si>
   <si>
     <t>B0GJDH8XTW</t>
   </si>
   <si>
-    <t>PureMatt Pro 35Kpa Max Suction AI Mattress Vacuum [100% Allergen, Dust &amp; Pet Hair Removal] Bed Vacuum Cleaner with UV Lights,</t>
+    <t>Colour Name: Starry Gray</t>
+  </si>
+  <si>
+    <t>Brand: RANVOO | Special feature: UV Light, HEPA, High Precision Sensors, Ultrasonic Technology, Rapid Heating | Filter type: HEPA Filter | Surface recommendation: TOP 1 in New Releases | Power source: Corded Electric</t>
+  </si>
+  <si>
+    <t>RANVOO</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/stores/RANVOO/page/4598C590-4586-4B0D-914B-C8811A359BA2?lp_asin=B0GJDH8XTW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+  </si>
+  <si>
+    <t>PureMatt Pro 35Kpa Max Suction AI Mattress Vacuum [100% Allergen, Dust &amp; Pet Hair Removal] Bed Vacuum Cleaner with UV Lights, Ultrasonic, HEPA Filter &amp; Sensor, for Bed, Sofa,Carpet, Corded Starry Gray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Strongest 35kPA Dual Suction Clears 100% Allergens in One Go] Equipped with the latest 35Kpa dual suction mite and allergens removal system developed in 2024, it offers an astonishing 261% increase in suction power and a 300% larger suction area compared to the previous version. It effortlessly removes 100% of mites and allergens in one pass, solving problems like itching during sleep or nasal congestion. Give family the gift of a clean and comfortable night’s sleep.
+[Sextuple Tech in One to Achieve 100% Mites Inhibition] This bed vacuum cleaner uv sanitizing also equipped with a double-beating system of 12.8K beats per min, which will beat any bad substances in the mattress or sofa, such as dust and mites, to the surface through high-frequency beating, and then quickly suck them away. Medical-grade UV-C, ultrasonic waves and 65℃ heating system specifically designed for mites can completely kill mite eggs.
+[Pro-grade Air Purification With 6-Stage HEPA Filter and Negative Ions] RANVOO mattress vacuum is equipped with HEPA filter to achieve efficient filtration of millimeter-level particles, completely filtering out all inhaled dust, mites and allergens. RANVOO's exclusive negative oxygen ion air filtration system, which can promptly purify any dust and mites emitted from the mattress or sofa into the air when using a vacuum cleaner.
+[Easy to Use Even for Vacuum Beginners] RANVOO mattress cleaner does not require installation or any adjustments. You can start using it right after unpacking. The 400 ml large dust cup is enough to hold the dust generated by several full-house fabric cleanings, so there is no need to replace it frequently. Cleaning the dust cup and reinstalling it can also be done in tens of seconds. You can use it quickly and clean the whole house thoroughly without any tedious operations.
+[AI Chip Makes It the Best for All Fabrics] RANVOO bed vacuum is equipped with the most advanced AI chip, which can intelligently identify and adapt to any household fabrics such as mattresses, sofas, carpets and pillows, and automatically match the most suitable suction and amplitude to achieve the effect of completely removing mites and protecting the fabric itself on fabrics of different materials and depths.</t>
   </si>
   <si>
     <t>https://www.amazon.co.uk/dp/B0GJDH8XTW?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/711M2XsW1sL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/41-S5G-ONwL._AC_US200_.jpg</t>
+  </si>
+  <si>
+    <t>B0FX2VM7HM</t>
+  </si>
+  <si>
+    <t>28.9L x 33.8W x 18.8H centimetres</t>
   </si>
   <si>
     <t>B0D7HF8S2W</t>
   </si>
   <si>
-    <t>Minthouz Mattress Vacuum Cleaner with UV Light &amp; Dust Mite Sensor, Double Roller Handheld Futon Vacuum Bed Cleaner Machine wi</t>
+    <t>Colour Name: Matte Black</t>
+  </si>
+  <si>
+    <t>Brand: Minthouz | Special feature: Corded, HEPA, High Precision Sensors, UV Light | Filter type: HEPA Filter | Surface recommendation: mattress | Power source: Corded Electric</t>
+  </si>
+  <si>
+    <t>Minthouz</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/stores/Minthouz/page/10C1A6E0-EA82-42DE-BB39-8D8D80A76300?lp_asin=B0D7HF8S2W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+  </si>
+  <si>
+    <t>Minthouz Mattress Vacuum Cleaner with UV Light &amp; Dust Mite Sensor, Double Roller Handheld Futon Vacuum Bed Cleaner Machine with 2 HEPA, Heating &amp; Indicator Mite Vacuum Cleaner for Bed/Sofa/Mattress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【Say Hi to Health!】Minthouz mattress vacuum cleaner incorporates advanced Dust Sensing Technology and a Dust Indicator that allows you to easily spot areas that need to be cleaned.The 450W motor makes the dust mite remover smaller, lighter, quieter and still delivers MAX suction. Combined with dual rollers, 60°C hot air system and 253.7nm UVC lamp integrated design, NO more mites, but ONLY a healthy and clean environment.
+【Is cleaning equipment heavy and time-consuming?】 Under the premise of maintaining strong suction power equipped with high-power lightweight motor, the weight of the whole machine is about 3.6KG, and the aerodynamic streamlined design can make the bed vacuum cleaner push process more silky smooth to a certain extent. The large chassis design allows the one-time cleaning area to be enlarged by about 𝟭.𝟱 times (Max 500c㎡), which reduces your mattress cleaning time by about 𝟯𝟬% !
+【Worried about damaging mattress?】 Minthouz mite vacuum cleaner adopts double Air Duct &amp; Roller system, which not only reduces the probability of air duct clogging by 𝟱𝟬% from the root, but also makes a cleaning to achieve 𝟮 times the effect. 𝟮×60,000rpm high vibration frequency combined with soft rubber material brush, not only protect the bed sheet, but also most of the mites and dust will be slapped down and sucked into our mattress cleaner, which is mite allergy people absolute gospel!
+*𝗪𝗮𝗿𝗺 𝘁𝗶𝗽: 𝟭. Both of our roller brushes are equipped with double locking buttons, which effectively prevents the roller from coming loose and makes it easy for you to dismantle &amp; clean them at the same time. 𝟮. Our 300ml filter adopts three layers of high-efficiency protection to ensure that it will not cause secondary pollution, so it is also a disposable accessory. The display will indicate when filter is full. (Please refer to the enclosed instruction manual for more information)
+【Still plagued by monsoon humidity?】 Studies have shown that mites will thrive in humid environments at 30℃, and will die when the temperature is above 55℃. However, our vacuum provide hot air up to 60°C, which is enough to send the mites away from the Earth. Equipped with large air vent cooling system at the tail end, it can increase the cooling efficiency by about 𝟲𝟳%! (Tip: As the vacuum is made of advanced temperature-conducting material, the surface will inevitably warm up after long use)
+【Mite Buster】 Our dust mite vacuum cleaner is also designed to incorporate a UV Lamp Sterilization feature that provides light in the 253.7nm band, which combines powerful suction, dual roller &amp; hot wind system to remove up to 𝟵𝟵.𝟵𝟵% of mites. The dust mite sensor allows you to clearly see the area you need to focus on and the gravity sensing system automatically stops the UV light when the handheld vacuum is higher than 5cm or tilted 30° to give you the most comprehensive protection!</t>
   </si>
   <si>
     <t>https://www.amazon.co.uk/dp/B0D7HF8S2W?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/61BhZB73+YL._AC_UL300_SR300,200_.jpg</t>
-  </si>
-  <si>
-    <t>B0FPQMRBYZ</t>
-  </si>
-  <si>
-    <t>Kärcher Mattress cleaner VCH 4 UVClean, hygienic deep cleaning with UV-C light, knock roller and suction function, power 500</t>
-  </si>
-  <si>
-    <t>https://www.amazon.co.uk/dp/B0FPQMRBYZ?psc=1</t>
-  </si>
-  <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/81MMJHIRoeL._AC_UL300_SR300,200_.jpg</t>
-  </si>
-  <si>
-    <t>B0DSCSR4MB</t>
-  </si>
-  <si>
-    <t>HAUSHOF 400 W Mattress Vacuum Cleaner with 15 kPa Suction for Bed &amp; SofasMite Level Display, UV-C Light &amp; Hot Air &amp; Roller</t>
-  </si>
-  <si>
-    <t>https://www.amazon.co.uk/dp/B0DSCSR4MB?psc=1</t>
-  </si>
-  <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/71bpuKTUQQL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/31O99tSwr1L._AC_US200_.jpg</t>
+  </si>
+  <si>
+    <t>B0H8S6713Z</t>
+  </si>
+  <si>
+    <t>3.6 Kilograms</t>
+  </si>
+  <si>
+    <t>3.60 kg</t>
+  </si>
+  <si>
+    <t>26.2L x 17.5W x 25.5H centimetres</t>
   </si>
   <si>
     <t>B0F13NCPTZ</t>
   </si>
   <si>
-    <t>Bear Mattress Vacuum Cleaner, 15Kpa Suction &amp; 253.7nm UV-C Lamp Sterilization 5 in 1 Handheld Dust Mite Vacuum Cleaner, HEPA</t>
+    <t>Brand: Bear | Special feature: HEPA | Filter type: HEPA Filter | Surface recommendation: All floors | Power source: Battery Powered</t>
+  </si>
+  <si>
+    <t>Bear</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/Bear/b/ref=bl_dp_s_web_89011654031?ie=UTF8&amp;node=89011654031&amp;field-lbr_brands_browse-bin=Bear</t>
+  </si>
+  <si>
+    <t>Bear Mattress Vacuum Cleaner, 15Kpa Suction &amp; 253.7nm UV-C Lamp Sterilization 5 in 1 Handheld Dust Mite Vacuum Cleaner, HEPA Filter Dual-Container Handheld Futon Vacuum for Bedding, Sofa &amp; Pillows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【Enhanced Cleaning Performance】:15kPa mattress vacuum cleaner 5-in-1 Functions,(Tapping+Heat+Ultrasonic+UV-C Light+Vacuum), the professional bed vacuum cleaner timesavingly removes dust deep in the mattress.
+【Auto-Beating Technology for Deep Cleaning】：The high tapping frequency of 48,000 cpm/min can penetrate deep into the mattress, effectively shaking out deep-seated mites and debris. Experience a deeper, more thorough clean than ever before.
+【UV-C Surface Sanitization &amp; 55°C Hot Air Drying】：253.7nm UV-C light penetrates directly into fabrics，which activates only on surface contact for safe use. 55°C warm air flows during operation to reduce dampness，keeping your mattress fresh and hygienic.
+【HEPA Filtration &amp; Dual Dust Cups】：The five-layer design of the filtration system and HEPA filters ensures the cleanliness of the air. 500ml dual dust cup reducing the need for frequent emptying. Its design effectively separates dust and waste, preventing secondary contamination and ensuring a more hygienic cleaning experience
+【Essential Oil Compartment】：The bottom is equipped with an aromatherapy box for use with essential oils, which eliminates mites while freshening the air, leaving both the mattress and quilt with a pleasant fragrance.</t>
   </si>
   <si>
     <t>https://www.amazon.co.uk/dp/B0F13NCPTZ?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/612vIVIFq3L._AC_UL300_SR300,200_.jpg</t>
+    <t>https://images-na.ssl-images-amazon.com/images/I/612vIVIFq3L._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0FGXMYDNH</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>2025-05-07</t>
+  </si>
+  <si>
+    <t>Bear Official Store</t>
+  </si>
+  <si>
+    <t>Nanshan Guangdong 518057 CN</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2F3NLKIQATJ4E</t>
+  </si>
+  <si>
+    <t>2.16 kg</t>
+  </si>
+  <si>
+    <t>26L x 15.9W x 25H centimetres</t>
+  </si>
+  <si>
+    <t>31.1 x 29.3 x 19.4 cm</t>
+  </si>
+  <si>
+    <t>31.10 x 29.30 x 19.40 cm</t>
   </si>
   <si>
     <t>B0DSFM31F7</t>
   </si>
   <si>
-    <t>Tjean UV Mattress Vacuum Cleaner,Futon Vacuum Dust Mite Vacuum – Dual Dust Bin, UV-C&amp;Ultrasonic Mite Removal, HEPA Filter, He</t>
+    <t>Brand: Tjean | Special feature: HEPA, UV Light, Washable Filter | Filter type: HEPA Filter | Surface recommendation: Carpet | Power source: Corded Electric</t>
+  </si>
+  <si>
+    <t>Tjean</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/stores/TJEANLifeCleanCookBette/page/D57A3099-B34A-4AE2-BEED-A573440938CE?lp_asin=B0DSFM31F7&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+  </si>
+  <si>
+    <t>Tjean UV Mattress Vacuum Cleaner,Futon Vacuum Dust Mite Vacuum – Dual Dust Bin, UV-C&amp;Ultrasonic Mite Removal, HEPA Filter, Heated Air – Anti-Allergy Bed Cleaner for Mattresses, Sofas, Carpets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Clogging – Dual Dust Container Our mite vacuum features a dual-chamber dust container system that prevents dust buildup and maintains strong suction power. Effective filtration ensures hygienic cleaning.
+Mite-Free – UV-C Light &amp; Ultrasound Equipped with intelligent UV lamp and ultrasound technology, our vacuum removes up to 99.9% of mites and allergens. Automatic activation provides safe, chemical-free disinfection.
+Deep Cleaning – Tapping Function &amp; Hot Air The vibration tapping function loosens deeply embedded dust and mites, while the warm airflow reduces moisture and keeps mattresses hygienically dry — ideal for allergy sufferers.
+Clean Air – HEPA Filter &amp; Anti-Hair Brush The anti-hair brush head prevents hair tangling, while the HEPA filter reliably traps fine particles and allergens — ensuring clean air.
+Versatile – For Mattresses &amp; More Perfect for mattresses, sofas, carpets, and pet areas. Effectively removes mites, dust, and pet hair for a hygienically clean home.</t>
   </si>
   <si>
     <t>https://www.amazon.co.uk/dp/B0DSFM31F7?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/71k7WLBBcwL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://images-na.ssl-images-amazon.com/images/I/71k7WLBBcwL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>2025-04-16</t>
+  </si>
+  <si>
+    <t>TJean Store</t>
+  </si>
+  <si>
+    <t>杭州市 余杭区 浙江省 311100 CN</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A21G0QWAFKJ6UP</t>
+  </si>
+  <si>
+    <t>2.22 kg</t>
+  </si>
+  <si>
+    <t>24L x 19.5W x 28.5H centimetres</t>
+  </si>
+  <si>
+    <t>32.6 x 27.5 x 21.1 cm</t>
+  </si>
+  <si>
+    <t>32.60 x 27.50 x 21.10 cm</t>
   </si>
   <si>
     <t>B0CHMPZVZT</t>
   </si>
   <si>
-    <t>JIGOO J300 Dust Mite Vacuum Cleaner with Dust Mite Sensor and UV Light, 500 W, Smart LED Display, Allergy Sufferers, Removes</t>
+    <t>Brand: JIGOO | Special feature: Intelligent Mite Sensor, UV-C Light, Ultrasound Function | Filter type: Cartridge | Surface recommendation: Upholstery | Power source: Corded Electric</t>
+  </si>
+  <si>
+    <t>JIGOO</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/JIGOO/b/ref=bl_dp_s_web_94911024031?ie=UTF8&amp;node=94911024031&amp;field-lbr_brands_browse-bin=JIGOO</t>
+  </si>
+  <si>
+    <t>JIGOO J300 Dust Mite Vacuum Cleaner with Dust Mite Sensor and UV Light, 500 W, Smart LED Display, Allergy Sufferers, Removes 99.9% Allergens, for Mattresses, Beds and Sofas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【Powerful &amp; Effective Suction】: The JIGOO J300 Bed Vacuum Cleaner boasts a mighty 500W motor that features high efficiency, powerful suction, and great durability. With 500W power and 13KPa suction, this cleaning machine ensures deep and thorough cleaning. Its 205mm suction inlet allows you to effortlessly clean large furniture, such as king-sized beds and lengthy sofas.
+【99.9% Mite Elimination】: The JIGOO J300 Anti-Dust Mite Vacuum Cleaner releases UV rays at a wavelength of 253.7nm, effortlessly eradicating mite cells and eliminating 99.9% of mites and bacteria lurking inside the mattress. Meanwhile, it emits ultrasonic waves to disrupt mite nervous systems. For your safety, the UV light will automatically turn off when the machine is lifted to avoid harm to your eyes.
+【Smart Dust Mite Sensor &amp; Display】: The intelligent sensor accurately detects dust mites, presenting a precise dust mite index and cleaning status, revolutionizing your cleaning routine. When the cleaning status light turns green, it indicates that the cleaning has been completed.
+【Dual-Cup Design】: The JIGOO J300 Mite Vacuum Cleaner is designed with 2 cups - one dedicated to filtration and the other to dust storage. The innovative dual-cup system is specially engineered to effectively extract dust mites and other allergens from the air, ensuring optimal air filtration, avoiding filter clogging, and enabling long-lasting, powerful suction.
+【Sturdy Metal Brushroll】: The metal brushroll with flexible silicone strips taps fast and hard at 12,000 times per minute. Its consistent, forceful taps easily remove pesky dust mites from your mattress without harming fabrics.
+【55℃ Hot-Air Dehumidification】: The JIGOO J300 Mattress Vacuum Cleaner blows 55℃ hot air to reduce mite activity and dehumidify your mattress to create a hygienic sleeping environment. It transforms your bed into a sanctuary, ensuring a healthier and more refreshing slumber.</t>
   </si>
   <si>
     <t>https://www.amazon.co.uk/dp/B0CHMPZVZT?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/71FO+Ga+gLL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/51Y-O7KBSlL._AC_US200_.jpg</t>
+  </si>
+  <si>
+    <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Vacuums:Handheld Vacuums</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Futon Vacuums
+Handheld Vacuums</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11
+1404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recycled materials (Global Recycled Standard)
+Safer chemicals (Global Recycled Standard)
+Worker well-being (Global Recycled Standard)</t>
+  </si>
+  <si>
+    <t>1.8 Kilograms</t>
+  </si>
+  <si>
+    <t>1.80 kg</t>
+  </si>
+  <si>
+    <t>28L x 24W x 20H centimetres</t>
   </si>
   <si>
     <t>B0D1QQXH6V</t>
   </si>
   <si>
-    <t>Bed Vacuum Cleaner - 5-in-1 Cordless Mattress Vacuum Cleaner, Powered by UV-C Light &amp; Ultrasonic Technology, 16Kpa Strong Suc</t>
+    <t>Brand: Amzany | Special feature: Cordless | Filter type: HEPA Filter | Surface recommendation: Carpet | Power source: Battery Powered</t>
+  </si>
+  <si>
+    <t>Amzany</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Amzany</t>
+  </si>
+  <si>
+    <t>Bed Vacuum Cleaner - 5-in-1 Cordless Mattress Vacuum Cleaner, Powered by UV-C Light &amp; Ultrasonic Technology, 16Kpa Strong Suction,Low Noise,Suitable for Dust, Pet Hair, Etc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Efficient cleaning performance: Amzany The most powerful anti-allergenic vacuum cleaner with a suction power of up to 16 kPa, stable power of 200 W to quickly absorb fine dust deep into the mattress.
+EFFICIENT &amp; FAST:With 253.7nm UV-C light, physics ultrasound, powerful high frequency knocking, hurricane deep breathing, super suction. The 5-in-1 quick cleaning method allows you to get the best mattress cleaning and provide you with a comprehensive and healthy environment.
+Full Environmental Humidity Monitoring Equipped with advanced monitoring function for the environment, it can detect the micro environment with high precision. The normal suitable humidity is 45%-65%. You can protect your home environment based on the displayed moisture values.
+Easy maintenance of HEPA filtration: The mattress vacuum cleaner comes with a HEPA filter and comes with 2 refills that filter 99.97% of particles up to 0.3 microns. Simply clean the dust box and filter it with tap water and let it dry. The device is still in use.
+【2 year replacement policy】We offer a 2-year product exchange policy. If you are not satisfied in any way when using our products, we promise to replace you with a new bed vacuum cleaner.</t>
   </si>
   <si>
     <t>https://www.amazon.co.uk/dp/B0D1QQXH6V?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/71PNQ3QEyHL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://images-na.ssl-images-amazon.com/images/I/71PNQ3QEyHL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0DBRWGZVR</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>2024-05-11</t>
+  </si>
+  <si>
+    <t>Amazon US</t>
+  </si>
+  <si>
+    <t>1.27 kg</t>
+  </si>
+  <si>
+    <t>24L x 23.1W x 12.4H centimetres</t>
+  </si>
+  <si>
+    <t>27.3 x 26.3 x 16.6 cm</t>
+  </si>
+  <si>
+    <t>27.30 x 26.30 x 16.60 cm</t>
   </si>
   <si>
     <t>B0F1XRXLVK</t>
   </si>
   <si>
-    <t>Gxzsk Mattress Vacuum Cleaner, 16kPa Bed Vacuum Cleaner with 253.7nm UV-C Light, Ultrasonic &amp; 140℉ Heating, Dual Cup &amp; Widen</t>
+    <t>Brand: Gxzsk | Special feature: 16KPA Strong Suction, Dual Cup &amp; Washable Filter, High Heating, UV Light &amp; Ultrasonic, Widen Suction Port &amp; Green Light Dust Display | Filter type: HEPA Filter | Surface recommendation: Mattress/Carpet/Fabric | Power source: Corded Electric</t>
+  </si>
+  <si>
+    <t>Gxzsk</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Gxzsk</t>
+  </si>
+  <si>
+    <t>Gxzsk Mattress Vacuum Cleaner, 16kPa Bed Vacuum Cleaner with 253.7nm UV-C Light, Ultrasonic &amp; 140℉ Heating, Dual Cup &amp; Widen Suction Port Handheld Vacuums for Bed, Sofa, Couch, Crib (500W, Corded)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🌀【16KPA POWERFUL SUCTION】This mattress vacuum cleaner is equipped with a 500W high-power motor that provides a powerful suction of 16kPa and high-speed vibration of 30000RPM. It can deeply penetrate through fabrics such as mattresses and sofas, shake the dust and debris inside the mattress to the surface, easily absorb hidden particles, allowing you to bid farewell to troubles such as sneezing completely. The strong suction can also easily absorb pet hair, keep the mattress clean, and create a comfortable living environment for you
+🛡️【UV-C LIGHT &amp; ULTRASONIC TECHNOLOGY】This multi-functional bed vacuum cleaner adopts a dual-effect purification technology of 253.7nm uv-c light and 40,000Hz ultrasonic waves. It penetrates deep into the mattress fibers, precisely capturing and removing 99.99% of invisible particles. This mattress cleaner also equipped with an intelligent safety system, its dual-wheel gravity sensor monitors contact surface in real time, uv-c light automatically activates only when placed horizontally and immediately deactivates when tilted or lifted, ensuring complete operational safety
+☀️【140℉ HOT AIR】This mattress vacuum cleaner is equipped with a powerful motor that continuously emits 140°F hot air, which penetrates the mattress fiber layers, destroy the living environment of harmful substances. The high-temperature hot air can also quickly evaporate the remaining moisture, keeping the mattress fresh and dry at all times, and creating a healthy and comfortable sleeping environment for you
+💡【WIDEN SUCTION PORT &amp; GREEN LIGHT DISPLAY】This mattress vacuum cleaner is equipped with an 8.7-inch widened suction port and a large-diameter anti-tangle roller brush. Combined with high-frequency beating technology, it can quickly separate embedded particles and complete the cleaning of the full-size bed in just 3 minutes. The extra-long 16.4FT power cord allows for free movement throughout the house. Paired with the intelligent green light dust display system, it can intuitively show the dust distribution in the cleaning area, saying goodbye to blind cleaning. This bed vacuum cleaner is truly a great helper for household cleaning
+💦【DUAL-CUP FILTERATION DESIGN】This handheld mattress cleaner features a dual-cup storage system, combining dual cyclone filtration and high-efficiency particulate filtration for enhanced performance. The 0.2L dust-separating cup captures hair and fibers, while the 0.4L dust-collecting cup stores debris, effectively preventing tangling. Equipped with a HEPA filter, it traps 99.99% of particles as small as 0.3 microns, preventing mattress vacuum cleaner from clogging, and extending service life. Both cups and filters are easily detachable and come with a cleaning brush for maintenance. After drying, they can be reused
+📢【NOTICE】This handheld mattress vacuum features automatic overheat protection. The roller brush is also equipped with anti-tangling protection, it will automatically stop when it gets tangled. Please clean the roller brush and filter promptly after use to prevent clogging and motor overheating. If the machine stops working, simply turn off the power and allow it to cool before resuming operation. Should you encounter any dissatisfaction while using this mattress vacuum cleaner, please don't hesitate to contact us, we're always happy to assist</t>
   </si>
   <si>
     <t>https://www.amazon.co.uk/dp/B0F1XRXLVK?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/7185wuCbHrL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/51vT9VPsfxL._AC_US200_.jpg</t>
+  </si>
+  <si>
+    <t>B0FFZWJTL1</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>25.1L x 29W x 14.7H centimetres</t>
   </si>
   <si>
     <t>B0D5WTVR91</t>
   </si>
   <si>
+    <t>Material: Plastic | Special feature: Cordless | Brand: OSALADI | Size: 11.00X8.50X6.00CMx3pcs | Manufacturer: OSALADI | Included components: towel rack | Model name: Futon Vacuums | Item weight: 147 Grams | Unit count: 1.0 count</t>
+  </si>
+  <si>
+    <t>OSALADI</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/stores/Convenienceforyourhome/page/818AA347-F8E9-4151-B8B2-A1E50E5C29AE?lp_asin=B0D5WTVR91&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+  </si>
+  <si>
     <t>OSALADI 3pcs Vacuum Wall Support Plastic Vacuum Holder for Wall Mounted Use Cordless Accessories Supports for Home Cleaning</t>
   </si>
   <si>
+    <t xml:space="preserve">Vacuum holder-- its innovative design allows you to hang the vacuum cleaner on the wall, saving space and creating a clutter- environment.
+Cordless vacuum accessories-- with its space-saving design, you can easily hang the vacuum cleaner on the wall, freeing up valuable floor space.
+Plastic vacuum holder-- made of plastic materials, it provides stable support for the vacuum cleaner and prevents it from falling.
+Wall mount for vacuum-- its durable design guarantees a long lifespan, making it a reliable and durable addition to your cleaning routine.
+Vacuum support-- its durable construction guarantees a product that can withstand daily use without getting damaged.</t>
+  </si>
+  <si>
     <t>https://www.amazon.co.uk/dp/B0D5WTVR91?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/41-H5-VQSVL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/31W1ZXCx81L._AC_US200_.jpg</t>
+  </si>
+  <si>
+    <t>B0D5WTH79H</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>147 Grams</t>
+  </si>
+  <si>
+    <t>147.00 g</t>
+  </si>
+  <si>
+    <t>11 x 8.5 x 18 centimetres</t>
   </si>
   <si>
     <t>导出时自动对相同ASIN去重。可能导致导出的产品总数与页面显示数量不一致</t>
@@ -413,9 +997,6 @@
   </si>
   <si>
     <t>市场份额</t>
-  </si>
-  <si>
-    <t>未知品牌</t>
   </si>
   <si>
     <t>卖家</t>
@@ -587,11 +1168,11 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -657,13 +1238,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -701,13 +1282,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -745,13 +1326,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -833,13 +1414,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1009,13 +1590,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1053,13 +1634,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1121,138 +1702,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="undefined">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="undefined">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Picture 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="undefined">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Picture 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1906,7 +2355,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="2" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A2" s="13">
         <v>1</v>
       </c>
@@ -1917,90 +2366,124 @@
         <v>71</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>70</v>
+        <v>73</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>74</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="M2" s="1"/>
+        <v>80</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N2" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q2" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O2" s="15">
+        <v>7167</v>
+      </c>
+      <c r="P2" s="15">
+        <v>1064</v>
+      </c>
+      <c r="Q2" s="16">
+        <v>0.12</v>
       </c>
       <c r="R2" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S2" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U2" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V2" s="15" t="s">
-        <v>70</v>
+        <v>84</v>
+      </c>
+      <c r="T2" s="15">
+        <v>658</v>
+      </c>
+      <c r="U2" s="16">
+        <v>-0.26</v>
+      </c>
+      <c r="V2" s="15">
+        <v>58562</v>
       </c>
       <c r="W2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="X2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z2" s="19">
+        <v>85</v>
+      </c>
+      <c r="X2" s="15">
+        <v>8900</v>
+      </c>
+      <c r="Y2" s="19">
+        <v>3</v>
+      </c>
+      <c r="Z2" s="20">
         <v>74.17</v>
       </c>
-      <c r="AD2" s="20">
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="2"/>
+      <c r="AD2" s="19">
         <v>540</v>
+      </c>
+      <c r="AE2" s="15">
+        <v>17</v>
       </c>
       <c r="AF2" s="21">
         <v>4.6</v>
       </c>
       <c r="AG2" s="22">
-        <v>0</v>
+        <v>0.0258</v>
+      </c>
+      <c r="AH2" s="20">
+        <v>3.43</v>
       </c>
       <c r="AI2" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK2" s="1"/>
-      <c r="AL2" s="20" t="s">
-        <v>70</v>
+        <v>0.96</v>
+      </c>
+      <c r="AK2" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL2" s="19">
+        <v>482</v>
+      </c>
+      <c r="AM2" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="AN2" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="AO2" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ2" s="20" t="s">
-        <v>70</v>
+      <c r="AP2" s="20">
+        <v>31</v>
+      </c>
+      <c r="AQ2" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR2" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS2" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT2" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="AU2" s="13" t="s">
         <v>70</v>
@@ -2015,7 +2498,7 @@
         <v>70</v>
       </c>
       <c r="AY2" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AZ2" s="13" t="s">
         <v>70</v>
@@ -2027,16 +2510,16 @@
         <v>70</v>
       </c>
       <c r="BC2" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BD2" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BE2" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF2" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BG2" s="13" t="s">
         <v>70</v>
@@ -2044,20 +2527,38 @@
       <c r="BH2" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BI2" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="BJ2" s="23" t="s">
+        <v>91</v>
+      </c>
       <c r="BK2" s="23" t="s">
-        <v>70</v>
+        <v>92</v>
+      </c>
+      <c r="BL2" s="23" t="s">
+        <v>93</v>
       </c>
       <c r="BM2" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN2" s="23" t="s">
+        <v>92</v>
+      </c>
       <c r="BO2" s="23" t="s">
-        <v>70</v>
+        <v>92</v>
+      </c>
+      <c r="BP2" s="23" t="s">
+        <v>94</v>
       </c>
       <c r="BQ2" s="23" t="s">
-        <v>70</v>
+        <v>95</v>
+      </c>
+      <c r="BR2" s="13" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="3" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" s="13">
         <v>2</v>
       </c>
@@ -2065,82 +2566,106 @@
         <v>70</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>70</v>
+        <v>98</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>99</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="M3" s="1"/>
+        <v>97</v>
+      </c>
+      <c r="M3" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N3" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q3" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O3" s="15">
+        <v>84997</v>
+      </c>
+      <c r="P3" s="15">
+        <v>-58472</v>
+      </c>
+      <c r="Q3" s="16">
+        <v>-0.79</v>
       </c>
       <c r="R3" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S3" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U3" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V3" s="15" t="s">
-        <v>70</v>
+        <v>105</v>
+      </c>
+      <c r="T3" s="15">
+        <v>90</v>
+      </c>
+      <c r="U3" s="16">
+        <v>0.78</v>
+      </c>
+      <c r="V3" s="15">
+        <v>17999</v>
       </c>
       <c r="W3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="X3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z3" s="4"/>
-      <c r="AD3" s="20">
-        <v>361</v>
+        <v>106</v>
+      </c>
+      <c r="X3" s="15">
+        <v>9841</v>
+      </c>
+      <c r="Y3" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="20">
+        <v>199.99</v>
+      </c>
+      <c r="AA3" s="4"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="2"/>
+      <c r="AD3" s="19">
+        <v>362</v>
+      </c>
+      <c r="AE3" s="15">
+        <v>15</v>
       </c>
       <c r="AF3" s="21">
         <v>4.6</v>
       </c>
       <c r="AG3" s="22">
-        <v>0</v>
+        <v>0.16670000000000001</v>
+      </c>
+      <c r="AH3" s="20">
+        <v>3.38</v>
       </c>
       <c r="AI3" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK3" s="1"/>
-      <c r="AL3" s="20" t="s">
-        <v>70</v>
+        <v>0.98</v>
+      </c>
+      <c r="AK3" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="AL3" s="19">
+        <v>572</v>
+      </c>
+      <c r="AM3" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AN3" s="13" t="s">
         <v>70</v>
@@ -2148,44 +2673,54 @@
       <c r="AO3" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ3" s="20" t="s">
-        <v>70</v>
+      <c r="AP3" s="4"/>
+      <c r="AQ3" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR3" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS3" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="AT3" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AU3" s="13" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AV3" s="14" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="AW3" s="13" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="AX3" s="13" t="s">
         <v>70</v>
       </c>
       <c r="AY3" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AZ3" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BA3" s="13" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="BB3" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BC3" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BD3" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BE3" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF3" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BG3" s="13" t="s">
         <v>70</v>
@@ -2193,20 +2728,38 @@
       <c r="BH3" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BI3" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="BJ3" s="23" t="s">
+        <v>114</v>
+      </c>
       <c r="BK3" s="23" t="s">
-        <v>70</v>
+        <v>115</v>
+      </c>
+      <c r="BL3" s="23" t="s">
+        <v>116</v>
       </c>
       <c r="BM3" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN3" s="23" t="s">
+        <v>117</v>
+      </c>
       <c r="BO3" s="23" t="s">
-        <v>70</v>
+        <v>118</v>
+      </c>
+      <c r="BP3" s="23" t="s">
+        <v>119</v>
       </c>
       <c r="BQ3" s="23" t="s">
-        <v>70</v>
+        <v>120</v>
+      </c>
+      <c r="BR3" s="13" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="4" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A4" s="13">
         <v>3</v>
       </c>
@@ -2214,59 +2767,64 @@
         <v>70</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>70</v>
+        <v>123</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>124</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="H4" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="M4" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="I4" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="J4" s="14" t="s">
+      <c r="N4" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="O4" s="15">
+        <v>97594</v>
+      </c>
+      <c r="P4" s="15">
+        <v>-186800</v>
+      </c>
+      <c r="Q4" s="16">
+        <v>-1.92</v>
+      </c>
+      <c r="R4" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="L4" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="M4" s="1"/>
-      <c r="N4" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O4" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P4" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q4" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="R4" s="17" t="s">
-        <v>70</v>
-      </c>
       <c r="S4" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T4" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U4" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V4" s="15" t="s">
-        <v>70</v>
+        <v>131</v>
+      </c>
+      <c r="T4" s="15">
+        <v>60</v>
+      </c>
+      <c r="U4" s="16">
+        <v>1.25</v>
+      </c>
+      <c r="V4" s="15">
+        <v>5999</v>
       </c>
       <c r="W4" s="15" t="s">
         <v>70</v>
@@ -2274,22 +2832,41 @@
       <c r="X4" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z4" s="4"/>
-      <c r="AD4" s="20">
-        <v>31</v>
+      <c r="Y4" s="19">
+        <v>2</v>
+      </c>
+      <c r="Z4" s="20">
+        <v>99.99</v>
+      </c>
+      <c r="AA4" s="4"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="19">
+        <v>46</v>
+      </c>
+      <c r="AE4" s="15">
+        <v>0</v>
       </c>
       <c r="AF4" s="21">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AG4" s="22">
         <v>0</v>
       </c>
+      <c r="AH4" s="20">
+        <v>5.18</v>
+      </c>
       <c r="AI4" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="1"/>
-      <c r="AL4" s="20" t="s">
-        <v>70</v>
+        <v>0.95</v>
+      </c>
+      <c r="AK4" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="AL4" s="19">
+        <v>309</v>
+      </c>
+      <c r="AM4" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AN4" s="13" t="s">
         <v>70</v>
@@ -2297,44 +2874,54 @@
       <c r="AO4" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ4" s="20" t="s">
-        <v>70</v>
+      <c r="AP4" s="4"/>
+      <c r="AQ4" s="19">
+        <v>8</v>
+      </c>
+      <c r="AR4" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS4" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="AT4" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AU4" s="13" t="s">
-        <v>70</v>
+        <v>133</v>
       </c>
       <c r="AV4" s="14" t="s">
-        <v>70</v>
+        <v>134</v>
       </c>
       <c r="AW4" s="13" t="s">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="AX4" s="13" t="s">
         <v>70</v>
       </c>
       <c r="AY4" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AZ4" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BA4" s="13" t="s">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="BB4" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BC4" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BD4" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BE4" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF4" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BG4" s="13" t="s">
         <v>70</v>
@@ -2342,20 +2929,38 @@
       <c r="BH4" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BI4" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="BJ4" s="23" t="s">
+        <v>137</v>
+      </c>
       <c r="BK4" s="23" t="s">
-        <v>70</v>
+        <v>138</v>
+      </c>
+      <c r="BL4" s="23" t="s">
+        <v>139</v>
       </c>
       <c r="BM4" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN4" s="23" t="s">
+        <v>140</v>
+      </c>
       <c r="BO4" s="23" t="s">
-        <v>70</v>
+        <v>140</v>
+      </c>
+      <c r="BP4" s="23" t="s">
+        <v>141</v>
       </c>
       <c r="BQ4" s="23" t="s">
-        <v>70</v>
+        <v>142</v>
+      </c>
+      <c r="BR4" s="13" t="s">
+        <v>143</v>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="5" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
         <v>4</v>
       </c>
@@ -2363,56 +2968,61 @@
         <v>70</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>70</v>
+        <v>145</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>146</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>72</v>
+        <v>147</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>85</v>
+        <v>148</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>70</v>
+        <v>149</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>87</v>
+        <v>151</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="M5" s="1"/>
+        <v>144</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N5" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O5" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P5" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q5" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O5" s="15">
+        <v>339242</v>
+      </c>
+      <c r="P5" s="15">
+        <v>-27530</v>
+      </c>
+      <c r="Q5" s="16">
+        <v>-0.02</v>
       </c>
       <c r="R5" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S5" s="18" t="s">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="T5" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="U5" s="16" t="s">
-        <v>70</v>
+      <c r="U5" s="16">
+        <v>-1</v>
       </c>
       <c r="V5" s="15" t="s">
         <v>70</v>
@@ -2423,22 +3033,41 @@
       <c r="X5" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z5" s="4"/>
-      <c r="AD5" s="20">
-        <v>46</v>
+      <c r="Y5" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="20">
+        <v>142.98</v>
+      </c>
+      <c r="AA5" s="4"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="2"/>
+      <c r="AD5" s="19">
+        <v>196</v>
+      </c>
+      <c r="AE5" s="15">
+        <v>19</v>
       </c>
       <c r="AF5" s="21">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AG5" s="22">
         <v>0</v>
       </c>
+      <c r="AH5" s="20">
+        <v>3.43</v>
+      </c>
       <c r="AI5" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="1"/>
-      <c r="AL5" s="20" t="s">
-        <v>70</v>
+        <v>0.98</v>
+      </c>
+      <c r="AK5" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="AL5" s="19">
+        <v>298</v>
+      </c>
+      <c r="AM5" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AN5" s="13" t="s">
         <v>70</v>
@@ -2446,17 +3075,27 @@
       <c r="AO5" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ5" s="20" t="s">
-        <v>70</v>
+      <c r="AP5" s="4"/>
+      <c r="AQ5" s="19">
+        <v>9</v>
+      </c>
+      <c r="AR5" s="19">
+        <v>2</v>
+      </c>
+      <c r="AS5" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="AT5" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AU5" s="13" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AV5" s="14" t="s">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="AW5" s="13" t="s">
-        <v>70</v>
+        <v>156</v>
       </c>
       <c r="AX5" s="13" t="s">
         <v>70</v>
@@ -2491,20 +3130,35 @@
       <c r="BH5" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ5" s="23" t="s">
+        <v>157</v>
+      </c>
       <c r="BK5" s="23" t="s">
-        <v>70</v>
+        <v>158</v>
+      </c>
+      <c r="BL5" s="23" t="s">
+        <v>159</v>
       </c>
       <c r="BM5" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN5" s="23" t="s">
+        <v>160</v>
+      </c>
       <c r="BO5" s="23" t="s">
-        <v>70</v>
+        <v>161</v>
+      </c>
+      <c r="BP5" s="23" t="s">
+        <v>162</v>
       </c>
       <c r="BQ5" s="23" t="s">
-        <v>70</v>
+        <v>163</v>
+      </c>
+      <c r="BR5" s="13" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="6" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A6" s="13">
         <v>5</v>
       </c>
@@ -2512,7 +3166,7 @@
         <v>70</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>88</v>
+        <v>164</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>70</v>
@@ -2520,42 +3174,44 @@
       <c r="E6" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="F6" s="14" t="s">
+        <v>165</v>
+      </c>
       <c r="G6" s="14" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>89</v>
+        <v>167</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>90</v>
+        <v>169</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>91</v>
+        <v>170</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="M6" s="1"/>
+        <v>164</v>
+      </c>
+      <c r="M6" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N6" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O6" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P6" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q6" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O6" s="15">
+        <v>125961</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>0</v>
       </c>
       <c r="R6" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S6" s="18" t="s">
-        <v>70</v>
+        <v>171</v>
       </c>
       <c r="T6" s="15" t="s">
         <v>70</v>
@@ -2572,9 +3228,15 @@
       <c r="X6" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="Y6" s="19">
+        <v>1</v>
+      </c>
       <c r="Z6" s="4"/>
-      <c r="AD6" s="20">
-        <v>30</v>
+      <c r="AA6" s="4"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="2"/>
+      <c r="AD6" s="19">
+        <v>31</v>
       </c>
       <c r="AF6" s="21">
         <v>4.4</v>
@@ -2585,9 +3247,14 @@
       <c r="AI6" s="16">
         <v>0</v>
       </c>
-      <c r="AK6" s="1"/>
-      <c r="AL6" s="20" t="s">
-        <v>70</v>
+      <c r="AK6" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="AL6" s="19">
+        <v>436</v>
+      </c>
+      <c r="AM6" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AN6" s="13" t="s">
         <v>70</v>
@@ -2595,8 +3262,14 @@
       <c r="AO6" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ6" s="20" t="s">
-        <v>70</v>
+      <c r="AP6" s="4"/>
+      <c r="AQ6" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR6" s="2"/>
+      <c r="AS6" s="1"/>
+      <c r="AT6" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AU6" s="13" t="s">
         <v>70</v>
@@ -2623,16 +3296,16 @@
         <v>70</v>
       </c>
       <c r="BC6" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BD6" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BE6" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF6" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BG6" s="13" t="s">
         <v>70</v>
@@ -2640,20 +3313,29 @@
       <c r="BH6" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ6" s="23" t="s">
+        <v>173</v>
+      </c>
       <c r="BK6" s="23" t="s">
-        <v>70</v>
+        <v>173</v>
+      </c>
+      <c r="BL6" s="23" t="s">
+        <v>174</v>
       </c>
       <c r="BM6" s="23" t="s">
-        <v>70</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="BN6" s="1"/>
       <c r="BO6" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP6" s="1"/>
       <c r="BQ6" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR6" s="1"/>
     </row>
-    <row r="7" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="7" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A7" s="13">
         <v>6</v>
       </c>
@@ -2661,7 +3343,7 @@
         <v>70</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>92</v>
+        <v>176</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>70</v>
@@ -2669,42 +3351,44 @@
       <c r="E7" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="F7" s="14" t="s">
+        <v>165</v>
+      </c>
       <c r="G7" s="14" t="s">
-        <v>72</v>
+        <v>177</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>93</v>
+        <v>178</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>70</v>
+        <v>179</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>94</v>
+        <v>180</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="M7" s="1"/>
+        <v>176</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N7" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O7" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P7" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q7" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O7" s="15">
+        <v>376778</v>
+      </c>
+      <c r="Q7" s="16">
+        <v>0</v>
       </c>
       <c r="R7" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S7" s="18" t="s">
-        <v>70</v>
+        <v>182</v>
       </c>
       <c r="T7" s="15" t="s">
         <v>70</v>
@@ -2721,14 +3405,18 @@
       <c r="X7" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z7" s="19">
-        <v>19.52</v>
-      </c>
-      <c r="AD7" s="20">
-        <v>87</v>
+      <c r="Y7" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="4"/>
+      <c r="AA7" s="4"/>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="2"/>
+      <c r="AD7" s="19">
+        <v>20</v>
       </c>
       <c r="AF7" s="21">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AG7" s="22">
         <v>0</v>
@@ -2736,9 +3424,14 @@
       <c r="AI7" s="16">
         <v>0</v>
       </c>
-      <c r="AK7" s="1"/>
-      <c r="AL7" s="20" t="s">
-        <v>70</v>
+      <c r="AK7" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="AL7" s="19">
+        <v>460</v>
+      </c>
+      <c r="AM7" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AN7" s="13" t="s">
         <v>70</v>
@@ -2746,8 +3439,14 @@
       <c r="AO7" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ7" s="20" t="s">
-        <v>70</v>
+      <c r="AP7" s="4"/>
+      <c r="AQ7" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR7" s="2"/>
+      <c r="AS7" s="1"/>
+      <c r="AT7" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AU7" s="13" t="s">
         <v>70</v>
@@ -2774,16 +3473,16 @@
         <v>70</v>
       </c>
       <c r="BC7" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BD7" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BE7" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF7" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BG7" s="13" t="s">
         <v>70</v>
@@ -2791,20 +3490,29 @@
       <c r="BH7" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ7" s="23" t="s">
+        <v>184</v>
+      </c>
       <c r="BK7" s="23" t="s">
-        <v>70</v>
+        <v>184</v>
+      </c>
+      <c r="BL7" s="23" t="s">
+        <v>185</v>
       </c>
       <c r="BM7" s="23" t="s">
-        <v>70</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="BN7" s="1"/>
       <c r="BO7" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP7" s="1"/>
       <c r="BQ7" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR7" s="1"/>
     </row>
-    <row r="8" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="8" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A8" s="13">
         <v>7</v>
       </c>
@@ -2812,50 +3520,52 @@
         <v>70</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>96</v>
+        <v>187</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>70</v>
+        <v>188</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>70</v>
+        <v>189</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>190</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>72</v>
+        <v>191</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>97</v>
+        <v>192</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>70</v>
+        <v>193</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>98</v>
+        <v>194</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>99</v>
+        <v>195</v>
       </c>
       <c r="L8" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="M8" s="1"/>
+        <v>196</v>
+      </c>
+      <c r="M8" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N8" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O8" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P8" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q8" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O8" s="15">
+        <v>313519</v>
+      </c>
+      <c r="Q8" s="16">
+        <v>0</v>
       </c>
       <c r="R8" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S8" s="18" t="s">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="T8" s="15" t="s">
         <v>70</v>
@@ -2872,12 +3582,18 @@
       <c r="X8" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="Y8" s="19">
+        <v>1</v>
+      </c>
       <c r="Z8" s="4"/>
-      <c r="AD8" s="20">
-        <v>195</v>
+      <c r="AA8" s="4"/>
+      <c r="AB8" s="1"/>
+      <c r="AC8" s="2"/>
+      <c r="AD8" s="19">
+        <v>30</v>
       </c>
       <c r="AF8" s="21">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AG8" s="22">
         <v>0</v>
@@ -2886,8 +3602,11 @@
         <v>0</v>
       </c>
       <c r="AK8" s="1"/>
-      <c r="AL8" s="20" t="s">
-        <v>70</v>
+      <c r="AL8" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM8" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AN8" s="13" t="s">
         <v>70</v>
@@ -2895,8 +3614,14 @@
       <c r="AO8" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ8" s="20" t="s">
-        <v>70</v>
+      <c r="AP8" s="4"/>
+      <c r="AQ8" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR8" s="2"/>
+      <c r="AS8" s="1"/>
+      <c r="AT8" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AU8" s="13" t="s">
         <v>70</v>
@@ -2923,7 +3648,7 @@
         <v>70</v>
       </c>
       <c r="BC8" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BD8" s="13" t="s">
         <v>70</v>
@@ -2932,7 +3657,7 @@
         <v>70</v>
       </c>
       <c r="BF8" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BG8" s="13" t="s">
         <v>70</v>
@@ -2940,20 +3665,27 @@
       <c r="BH8" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ8" s="1"/>
       <c r="BK8" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BL8" s="23" t="s">
+        <v>197</v>
+      </c>
       <c r="BM8" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN8" s="1"/>
       <c r="BO8" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP8" s="1"/>
       <c r="BQ8" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR8" s="1"/>
     </row>
-    <row r="9" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="9" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A9" s="13">
         <v>8</v>
       </c>
@@ -2961,50 +3693,52 @@
         <v>70</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>100</v>
+        <v>198</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>70</v>
+        <v>199</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>70</v>
+        <v>200</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>201</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>72</v>
+        <v>202</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>101</v>
+        <v>203</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>102</v>
+        <v>205</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>103</v>
+        <v>206</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="M9" s="1"/>
+        <v>207</v>
+      </c>
+      <c r="M9" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N9" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O9" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P9" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q9" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O9" s="15">
+        <v>333633</v>
+      </c>
+      <c r="Q9" s="16">
+        <v>0</v>
       </c>
       <c r="R9" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S9" s="18" t="s">
-        <v>70</v>
+        <v>182</v>
       </c>
       <c r="T9" s="15" t="s">
         <v>70</v>
@@ -3021,12 +3755,20 @@
       <c r="X9" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z9" s="4"/>
-      <c r="AD9" s="20">
-        <v>20</v>
+      <c r="Y9" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="20">
+        <v>19.52</v>
+      </c>
+      <c r="AA9" s="4"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="2"/>
+      <c r="AD9" s="19">
+        <v>87</v>
       </c>
       <c r="AF9" s="21">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AG9" s="22">
         <v>0</v>
@@ -3035,17 +3777,32 @@
         <v>0</v>
       </c>
       <c r="AK9" s="1"/>
-      <c r="AL9" s="20" t="s">
-        <v>70</v>
+      <c r="AL9" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM9" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="AN9" s="13" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="AO9" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ9" s="20" t="s">
-        <v>70</v>
+      <c r="AP9" s="20">
+        <v>51.92</v>
+      </c>
+      <c r="AQ9" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR9" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS9" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT9" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="AU9" s="13" t="s">
         <v>70</v>
@@ -3072,10 +3829,10 @@
         <v>70</v>
       </c>
       <c r="BC9" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BD9" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BE9" s="13" t="s">
         <v>70</v>
@@ -3089,20 +3846,29 @@
       <c r="BH9" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ9" s="23" t="s">
+        <v>208</v>
+      </c>
       <c r="BK9" s="23" t="s">
-        <v>70</v>
+        <v>209</v>
+      </c>
+      <c r="BL9" s="23" t="s">
+        <v>210</v>
       </c>
       <c r="BM9" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN9" s="1"/>
       <c r="BO9" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP9" s="1"/>
       <c r="BQ9" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR9" s="1"/>
     </row>
-    <row r="10" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="10" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A10" s="13">
         <v>9</v>
       </c>
@@ -3110,59 +3876,64 @@
         <v>70</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>104</v>
+        <v>211</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>70</v>
+        <v>212</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>213</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>72</v>
+        <v>214</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>105</v>
+        <v>215</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>70</v>
+        <v>216</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>106</v>
+        <v>217</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>107</v>
+        <v>218</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="M10" s="1"/>
+        <v>219</v>
+      </c>
+      <c r="M10" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N10" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O10" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P10" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q10" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O10" s="15">
+        <v>466967</v>
+      </c>
+      <c r="P10" s="15">
+        <v>40677</v>
+      </c>
+      <c r="Q10" s="16">
+        <v>0.09</v>
       </c>
       <c r="R10" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S10" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="T10" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="U10" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="V10" s="15" t="s">
-        <v>70</v>
+        <v>220</v>
+      </c>
+      <c r="T10" s="15">
+        <v>6</v>
+      </c>
+      <c r="U10" s="16">
+        <v>0</v>
+      </c>
+      <c r="V10" s="15">
+        <v>270</v>
       </c>
       <c r="W10" s="15" t="s">
         <v>70</v>
@@ -3170,22 +3941,41 @@
       <c r="X10" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z10" s="4"/>
-      <c r="AD10" s="20">
-        <v>199</v>
+      <c r="Y10" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="20">
+        <v>44.99</v>
+      </c>
+      <c r="AA10" s="4"/>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="2"/>
+      <c r="AD10" s="19">
+        <v>200</v>
+      </c>
+      <c r="AE10" s="15">
+        <v>4</v>
       </c>
       <c r="AF10" s="21">
         <v>4.4</v>
       </c>
       <c r="AG10" s="22">
-        <v>0</v>
+        <v>0.6667000000000001</v>
+      </c>
+      <c r="AH10" s="20">
+        <v>3.42</v>
       </c>
       <c r="AI10" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="1"/>
-      <c r="AL10" s="20" t="s">
-        <v>70</v>
+        <v>0.92</v>
+      </c>
+      <c r="AK10" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="AL10" s="19">
+        <v>509</v>
+      </c>
+      <c r="AM10" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AN10" s="13" t="s">
         <v>70</v>
@@ -3193,17 +3983,27 @@
       <c r="AO10" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ10" s="20" t="s">
-        <v>70</v>
+      <c r="AP10" s="4"/>
+      <c r="AQ10" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR10" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS10" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="AT10" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AU10" s="13" t="s">
-        <v>70</v>
+        <v>133</v>
       </c>
       <c r="AV10" s="14" t="s">
-        <v>70</v>
+        <v>223</v>
       </c>
       <c r="AW10" s="13" t="s">
-        <v>70</v>
+        <v>224</v>
       </c>
       <c r="AX10" s="13" t="s">
         <v>70</v>
@@ -3221,16 +4021,16 @@
         <v>70</v>
       </c>
       <c r="BC10" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BD10" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BE10" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF10" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BG10" s="13" t="s">
         <v>70</v>
@@ -3238,20 +4038,35 @@
       <c r="BH10" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ10" s="23" t="s">
+        <v>225</v>
+      </c>
       <c r="BK10" s="23" t="s">
-        <v>70</v>
+        <v>225</v>
+      </c>
+      <c r="BL10" s="23" t="s">
+        <v>226</v>
       </c>
       <c r="BM10" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN10" s="23" t="s">
+        <v>225</v>
+      </c>
       <c r="BO10" s="23" t="s">
-        <v>70</v>
+        <v>225</v>
+      </c>
+      <c r="BP10" s="23" t="s">
+        <v>227</v>
       </c>
       <c r="BQ10" s="23" t="s">
-        <v>70</v>
+        <v>228</v>
+      </c>
+      <c r="BR10" s="13" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="11" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
         <v>10</v>
       </c>
@@ -3259,50 +4074,55 @@
         <v>70</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>108</v>
+        <v>229</v>
       </c>
       <c r="D11" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>70</v>
+        <v>230</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>231</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>72</v>
+        <v>232</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>109</v>
+        <v>233</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>70</v>
+        <v>234</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>110</v>
+        <v>235</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>111</v>
+        <v>236</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="M11" s="1"/>
+        <v>229</v>
+      </c>
+      <c r="M11" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N11" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O11" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P11" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q11" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O11" s="15">
+        <v>778522</v>
+      </c>
+      <c r="P11" s="15">
+        <v>16609</v>
+      </c>
+      <c r="Q11" s="16">
+        <v>0.02</v>
       </c>
       <c r="R11" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S11" s="18" t="s">
-        <v>70</v>
+        <v>237</v>
       </c>
       <c r="T11" s="15" t="s">
         <v>70</v>
@@ -3319,9 +4139,20 @@
       <c r="X11" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z11" s="4"/>
-      <c r="AD11" s="20">
+      <c r="Y11" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="20">
+        <v>46.8</v>
+      </c>
+      <c r="AA11" s="4"/>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="2"/>
+      <c r="AD11" s="19">
         <v>29</v>
+      </c>
+      <c r="AE11" s="15">
+        <v>0</v>
       </c>
       <c r="AF11" s="21">
         <v>4.6</v>
@@ -3329,12 +4160,20 @@
       <c r="AG11" s="22">
         <v>0</v>
       </c>
+      <c r="AH11" s="20">
+        <v>3.42</v>
+      </c>
       <c r="AI11" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="1"/>
-      <c r="AL11" s="20" t="s">
-        <v>70</v>
+        <v>0.93</v>
+      </c>
+      <c r="AK11" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="AL11" s="19">
+        <v>530</v>
+      </c>
+      <c r="AM11" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AN11" s="13" t="s">
         <v>70</v>
@@ -3342,17 +4181,27 @@
       <c r="AO11" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ11" s="20" t="s">
-        <v>70</v>
+      <c r="AP11" s="4"/>
+      <c r="AQ11" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR11" s="19">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="AT11" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AU11" s="13" t="s">
-        <v>70</v>
+        <v>133</v>
       </c>
       <c r="AV11" s="14" t="s">
-        <v>70</v>
+        <v>240</v>
       </c>
       <c r="AW11" s="13" t="s">
-        <v>70</v>
+        <v>241</v>
       </c>
       <c r="AX11" s="13" t="s">
         <v>70</v>
@@ -3370,16 +4219,16 @@
         <v>70</v>
       </c>
       <c r="BC11" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BD11" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BE11" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF11" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BG11" s="13" t="s">
         <v>70</v>
@@ -3387,20 +4236,35 @@
       <c r="BH11" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ11" s="23" t="s">
+        <v>242</v>
+      </c>
       <c r="BK11" s="23" t="s">
-        <v>70</v>
+        <v>242</v>
+      </c>
+      <c r="BL11" s="23" t="s">
+        <v>243</v>
       </c>
       <c r="BM11" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN11" s="23" t="s">
+        <v>242</v>
+      </c>
       <c r="BO11" s="23" t="s">
-        <v>70</v>
+        <v>242</v>
+      </c>
+      <c r="BP11" s="23" t="s">
+        <v>244</v>
       </c>
       <c r="BQ11" s="23" t="s">
-        <v>70</v>
+        <v>245</v>
+      </c>
+      <c r="BR11" s="13" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="12" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="12" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
         <v>11</v>
       </c>
@@ -3408,50 +4272,52 @@
         <v>70</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>112</v>
+        <v>246</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>70</v>
+        <v>247</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>248</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>72</v>
+        <v>249</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>113</v>
+        <v>250</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>70</v>
+        <v>251</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>114</v>
+        <v>252</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>115</v>
+        <v>253</v>
       </c>
       <c r="L12" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="M12" s="1"/>
+        <v>246</v>
+      </c>
+      <c r="M12" s="14" t="s">
+        <v>254</v>
+      </c>
       <c r="N12" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O12" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P12" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q12" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O12" s="15">
+        <v>1372634</v>
+      </c>
+      <c r="Q12" s="16">
+        <v>0</v>
       </c>
       <c r="R12" s="17" t="s">
-        <v>70</v>
+        <v>255</v>
       </c>
       <c r="S12" s="18" t="s">
-        <v>70</v>
+        <v>256</v>
       </c>
       <c r="T12" s="15" t="s">
         <v>70</v>
@@ -3468,8 +4334,14 @@
       <c r="X12" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="Y12" s="19">
+        <v>1</v>
+      </c>
       <c r="Z12" s="4"/>
-      <c r="AD12" s="20">
+      <c r="AA12" s="4"/>
+      <c r="AB12" s="1"/>
+      <c r="AC12" s="2"/>
+      <c r="AD12" s="19">
         <v>254</v>
       </c>
       <c r="AF12" s="21">
@@ -3482,8 +4354,11 @@
         <v>0</v>
       </c>
       <c r="AK12" s="1"/>
-      <c r="AL12" s="20" t="s">
-        <v>70</v>
+      <c r="AL12" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM12" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AN12" s="13" t="s">
         <v>70</v>
@@ -3491,8 +4366,14 @@
       <c r="AO12" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ12" s="20" t="s">
-        <v>70</v>
+      <c r="AP12" s="4"/>
+      <c r="AQ12" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR12" s="2"/>
+      <c r="AS12" s="1"/>
+      <c r="AT12" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AU12" s="13" t="s">
         <v>70</v>
@@ -3510,25 +4391,25 @@
         <v>70</v>
       </c>
       <c r="AZ12" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BA12" s="13" t="s">
-        <v>70</v>
+        <v>257</v>
       </c>
       <c r="BB12" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BC12" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BD12" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BE12" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF12" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BG12" s="13" t="s">
         <v>70</v>
@@ -3536,20 +4417,29 @@
       <c r="BH12" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ12" s="23" t="s">
+        <v>258</v>
+      </c>
       <c r="BK12" s="23" t="s">
-        <v>70</v>
+        <v>259</v>
+      </c>
+      <c r="BL12" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="BM12" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN12" s="1"/>
       <c r="BO12" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP12" s="1"/>
       <c r="BQ12" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR12" s="1"/>
     </row>
-    <row r="13" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="13" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A13" s="13">
         <v>12</v>
       </c>
@@ -3557,56 +4447,59 @@
         <v>70</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>116</v>
+        <v>261</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>70</v>
+        <v>262</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>263</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>72</v>
+        <v>264</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>117</v>
+        <v>265</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>70</v>
+        <v>266</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>118</v>
+        <v>267</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>119</v>
+        <v>268</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="M13" s="1"/>
+        <v>269</v>
+      </c>
+      <c r="M13" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N13" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O13" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P13" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q13" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O13" s="15">
+        <v>2655457</v>
+      </c>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="16">
+        <v>0</v>
       </c>
       <c r="R13" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S13" s="18" t="s">
-        <v>70</v>
+        <v>270</v>
       </c>
       <c r="T13" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="U13" s="16" t="s">
-        <v>70</v>
+      <c r="U13" s="16">
+        <v>-1</v>
       </c>
       <c r="V13" s="15" t="s">
         <v>70</v>
@@ -3617,9 +4510,20 @@
       <c r="X13" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z13" s="4"/>
-      <c r="AD13" s="20">
+      <c r="Y13" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="20">
+        <v>91.74</v>
+      </c>
+      <c r="AA13" s="4"/>
+      <c r="AB13" s="1"/>
+      <c r="AC13" s="2"/>
+      <c r="AD13" s="19">
         <v>1120</v>
+      </c>
+      <c r="AE13" s="15">
+        <v>213</v>
       </c>
       <c r="AF13" s="21">
         <v>3.9</v>
@@ -3627,12 +4531,20 @@
       <c r="AG13" s="22">
         <v>0</v>
       </c>
+      <c r="AH13" s="20">
+        <v>3.64</v>
+      </c>
       <c r="AI13" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="1"/>
-      <c r="AL13" s="20" t="s">
-        <v>70</v>
+        <v>0.96</v>
+      </c>
+      <c r="AK13" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="AL13" s="19">
+        <v>870</v>
+      </c>
+      <c r="AM13" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AN13" s="13" t="s">
         <v>70</v>
@@ -3640,8 +4552,18 @@
       <c r="AO13" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ13" s="20" t="s">
-        <v>70</v>
+      <c r="AP13" s="4"/>
+      <c r="AQ13" s="19">
+        <v>8</v>
+      </c>
+      <c r="AR13" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS13" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="AT13" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AU13" s="13" t="s">
         <v>70</v>
@@ -3685,20 +4607,35 @@
       <c r="BH13" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ13" s="23" t="s">
+        <v>273</v>
+      </c>
       <c r="BK13" s="23" t="s">
-        <v>70</v>
+        <v>273</v>
+      </c>
+      <c r="BL13" s="23" t="s">
+        <v>274</v>
       </c>
       <c r="BM13" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN13" s="23" t="s">
+        <v>273</v>
+      </c>
       <c r="BO13" s="23" t="s">
-        <v>70</v>
+        <v>273</v>
+      </c>
+      <c r="BP13" s="23" t="s">
+        <v>275</v>
       </c>
       <c r="BQ13" s="23" t="s">
-        <v>70</v>
+        <v>276</v>
+      </c>
+      <c r="BR13" s="13" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="14" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A14" s="13">
         <v>13</v>
       </c>
@@ -3706,50 +4643,52 @@
         <v>70</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>120</v>
+        <v>277</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>70</v>
+        <v>278</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>279</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>72</v>
+        <v>280</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>121</v>
+        <v>281</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>70</v>
+        <v>282</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>122</v>
+        <v>283</v>
       </c>
       <c r="K14" s="14" t="s">
-        <v>123</v>
+        <v>284</v>
       </c>
       <c r="L14" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="M14" s="1"/>
+        <v>285</v>
+      </c>
+      <c r="M14" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N14" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O14" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P14" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q14" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O14" s="15">
+        <v>3528062</v>
+      </c>
+      <c r="Q14" s="16">
+        <v>0</v>
       </c>
       <c r="R14" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S14" s="18" t="s">
-        <v>70</v>
+        <v>286</v>
       </c>
       <c r="T14" s="15" t="s">
         <v>70</v>
@@ -3766,8 +4705,14 @@
       <c r="X14" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="Y14" s="19">
+        <v>1</v>
+      </c>
       <c r="Z14" s="4"/>
-      <c r="AD14" s="20">
+      <c r="AA14" s="4"/>
+      <c r="AB14" s="1"/>
+      <c r="AC14" s="2"/>
+      <c r="AD14" s="19">
         <v>384</v>
       </c>
       <c r="AF14" s="21">
@@ -3780,8 +4725,11 @@
         <v>0</v>
       </c>
       <c r="AK14" s="1"/>
-      <c r="AL14" s="20" t="s">
-        <v>70</v>
+      <c r="AL14" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM14" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AN14" s="13" t="s">
         <v>70</v>
@@ -3789,8 +4737,14 @@
       <c r="AO14" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ14" s="20" t="s">
-        <v>70</v>
+      <c r="AP14" s="4"/>
+      <c r="AQ14" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR14" s="2"/>
+      <c r="AS14" s="1"/>
+      <c r="AT14" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AU14" s="13" t="s">
         <v>70</v>
@@ -3834,20 +4788,27 @@
       <c r="BH14" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ14" s="1"/>
       <c r="BK14" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BL14" s="23" t="s">
+        <v>287</v>
+      </c>
       <c r="BM14" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN14" s="1"/>
       <c r="BO14" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP14" s="1"/>
       <c r="BQ14" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR14" s="1"/>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="15" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
         <v>14</v>
       </c>
@@ -3855,50 +4816,52 @@
         <v>70</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>124</v>
+        <v>288</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>70</v>
+        <v>289</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>290</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>72</v>
+        <v>291</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>125</v>
+        <v>292</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>70</v>
+        <v>293</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>126</v>
+        <v>294</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>127</v>
+        <v>295</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="M15" s="1"/>
+        <v>296</v>
+      </c>
+      <c r="M15" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="N15" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O15" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P15" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q15" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
+      </c>
+      <c r="O15" s="15">
+        <v>3802207</v>
+      </c>
+      <c r="Q15" s="16">
+        <v>0</v>
       </c>
       <c r="R15" s="17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="S15" s="18" t="s">
-        <v>70</v>
+        <v>297</v>
       </c>
       <c r="T15" s="15" t="s">
         <v>70</v>
@@ -3915,7 +4878,13 @@
       <c r="X15" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="Y15" s="19">
+        <v>1</v>
+      </c>
       <c r="Z15" s="4"/>
+      <c r="AA15" s="4"/>
+      <c r="AB15" s="1"/>
+      <c r="AC15" s="2"/>
       <c r="AD15" s="2"/>
       <c r="AF15" s="5"/>
       <c r="AG15" s="22">
@@ -3925,8 +4894,11 @@
         <v>0</v>
       </c>
       <c r="AK15" s="1"/>
-      <c r="AL15" s="20" t="s">
-        <v>70</v>
+      <c r="AL15" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM15" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AN15" s="13" t="s">
         <v>70</v>
@@ -3934,8 +4906,14 @@
       <c r="AO15" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ15" s="20" t="s">
-        <v>70</v>
+      <c r="AP15" s="4"/>
+      <c r="AQ15" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR15" s="2"/>
+      <c r="AS15" s="1"/>
+      <c r="AT15" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="AU15" s="13" t="s">
         <v>70</v>
@@ -3962,10 +4940,10 @@
         <v>70</v>
       </c>
       <c r="BC15" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BD15" s="13" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BE15" s="13" t="s">
         <v>70</v>
@@ -3979,23 +4957,32 @@
       <c r="BH15" s="14" t="s">
         <v>70</v>
       </c>
+      <c r="BJ15" s="23" t="s">
+        <v>298</v>
+      </c>
       <c r="BK15" s="23" t="s">
-        <v>70</v>
+        <v>299</v>
+      </c>
+      <c r="BL15" s="23" t="s">
+        <v>300</v>
       </c>
       <c r="BM15" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BN15" s="1"/>
       <c r="BO15" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BP15" s="1"/>
       <c r="BQ15" s="23" t="s">
         <v>70</v>
       </c>
+      <c r="BR15" s="1"/>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A16" s="24"/>
       <c r="B16" s="24" t="s">
-        <v>128</v>
+        <v>301</v>
       </c>
       <c r="C16" s="24"/>
       <c r="D16" s="24"/>
@@ -4069,85 +5056,118 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" tooltip="https://www.amazon.co.uk/dp/B0FBH3FKJH"/>
-    <hyperlink ref="G2" r:id="rId2" tooltip="https://www.amazon.co.ukundefined"/>
+    <hyperlink ref="G2" r:id="rId2" tooltip="https://www.amazon.co.uk/stores/Hoover/page/93924FFB-1D83-4E54-8B26-4C7644C8FC3E?lp_asin=B0FBH3FKJH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
     <hyperlink ref="J2" r:id="rId3" tooltip="https://www.amazon.co.uk/dp/B0FBH3FKJH?psc=1"/>
-    <hyperlink ref="K2" r:id="rId4" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71mCoX81GcL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L2" r:id="rId5" tooltip="https://www.amazon.co.uk/dp/B0FBH3FKJH"/>
-    <hyperlink ref="C3" r:id="rId6" tooltip="https://www.amazon.co.uk/dp/B0DHL35LFT"/>
-    <hyperlink ref="G3" r:id="rId7" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J3" r:id="rId8" tooltip="https://www.amazon.co.uk/dp/B0DHL35LFT?psc=1"/>
-    <hyperlink ref="K3" r:id="rId9" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61Vef2rJE5L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L3" r:id="rId10" tooltip="https://www.amazon.co.uk/dp/B0DHL35LFT"/>
-    <hyperlink ref="C4" r:id="rId11" tooltip="https://www.amazon.co.uk/dp/B0DTS8VCFB"/>
-    <hyperlink ref="G4" r:id="rId12" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J4" r:id="rId13" tooltip="https://www.amazon.co.uk/dp/B0DTS8VCFB?psc=1"/>
-    <hyperlink ref="K4" r:id="rId14" tooltip="https://images-eu.ssl-images-amazon.com/images/I/616ONjp63mL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L4" r:id="rId15" tooltip="https://www.amazon.co.uk/dp/B0DTS8VCFB"/>
-    <hyperlink ref="C5" r:id="rId16" tooltip="https://www.amazon.co.uk/dp/B0FN3GPQZM"/>
-    <hyperlink ref="G5" r:id="rId17" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J5" r:id="rId18" tooltip="https://www.amazon.co.uk/dp/B0FN3GPQZM?psc=1"/>
-    <hyperlink ref="K5" r:id="rId19" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71zFBwnc9GL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L5" r:id="rId20" tooltip="https://www.amazon.co.uk/dp/B0FN3GPQZM"/>
-    <hyperlink ref="C6" r:id="rId21" tooltip="https://www.amazon.co.uk/dp/B0GJDH8XTW"/>
-    <hyperlink ref="G6" r:id="rId22" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J6" r:id="rId23" tooltip="https://www.amazon.co.uk/dp/B0GJDH8XTW?psc=1"/>
-    <hyperlink ref="K6" r:id="rId24" tooltip="https://images-eu.ssl-images-amazon.com/images/I/711M2XsW1sL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L6" r:id="rId25" tooltip="https://www.amazon.co.uk/dp/B0GJDH8XTW"/>
-    <hyperlink ref="C7" r:id="rId26" tooltip="https://www.amazon.co.uk/dp/B0D7HF8S2W"/>
-    <hyperlink ref="G7" r:id="rId27" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J7" r:id="rId28" tooltip="https://www.amazon.co.uk/dp/B0D7HF8S2W?psc=1"/>
-    <hyperlink ref="K7" r:id="rId29" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61BhZB73+YL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L7" r:id="rId30" tooltip="https://www.amazon.co.uk/dp/B0D7HF8S2W"/>
-    <hyperlink ref="C8" r:id="rId31" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ"/>
-    <hyperlink ref="G8" r:id="rId32" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J8" r:id="rId33" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ?psc=1"/>
-    <hyperlink ref="K8" r:id="rId34" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81MMJHIRoeL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L8" r:id="rId35" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ"/>
-    <hyperlink ref="C9" r:id="rId36" tooltip="https://www.amazon.co.uk/dp/B0DSCSR4MB"/>
-    <hyperlink ref="G9" r:id="rId37" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J9" r:id="rId38" tooltip="https://www.amazon.co.uk/dp/B0DSCSR4MB?psc=1"/>
-    <hyperlink ref="K9" r:id="rId39" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71bpuKTUQQL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L9" r:id="rId40" tooltip="https://www.amazon.co.uk/dp/B0DSCSR4MB"/>
-    <hyperlink ref="C10" r:id="rId41" tooltip="https://www.amazon.co.uk/dp/B0F13NCPTZ"/>
-    <hyperlink ref="G10" r:id="rId42" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J10" r:id="rId43" tooltip="https://www.amazon.co.uk/dp/B0F13NCPTZ?psc=1"/>
-    <hyperlink ref="K10" r:id="rId44" tooltip="https://images-eu.ssl-images-amazon.com/images/I/612vIVIFq3L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L10" r:id="rId45" tooltip="https://www.amazon.co.uk/dp/B0F13NCPTZ"/>
-    <hyperlink ref="C11" r:id="rId46" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7"/>
-    <hyperlink ref="G11" r:id="rId47" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J11" r:id="rId48" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7?psc=1"/>
-    <hyperlink ref="K11" r:id="rId49" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71k7WLBBcwL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L11" r:id="rId50" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7"/>
-    <hyperlink ref="C12" r:id="rId51" tooltip="https://www.amazon.co.uk/dp/B0CHMPZVZT"/>
-    <hyperlink ref="G12" r:id="rId52" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J12" r:id="rId53" tooltip="https://www.amazon.co.uk/dp/B0CHMPZVZT?psc=1"/>
-    <hyperlink ref="K12" r:id="rId54" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71FO+Ga+gLL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L12" r:id="rId55" tooltip="https://www.amazon.co.uk/dp/B0CHMPZVZT"/>
-    <hyperlink ref="C13" r:id="rId56" tooltip="https://www.amazon.co.uk/dp/B0D1QQXH6V"/>
-    <hyperlink ref="G13" r:id="rId57" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.co.uk/dp/B0D1QQXH6V?psc=1"/>
-    <hyperlink ref="K13" r:id="rId59" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71PNQ3QEyHL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.co.uk/dp/B0D1QQXH6V"/>
-    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK"/>
-    <hyperlink ref="G14" r:id="rId62" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK?psc=1"/>
-    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-eu.ssl-images-amazon.com/images/I/7185wuCbHrL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK"/>
-    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.co.uk/dp/B0D5WTVR91"/>
-    <hyperlink ref="G15" r:id="rId67" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.co.uk/dp/B0D5WTVR91?psc=1"/>
-    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-eu.ssl-images-amazon.com/images/I/41-H5-VQSVL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.co.uk/dp/B0D5WTVR91"/>
+    <hyperlink ref="K2" r:id="rId4" tooltip="https://m.media-amazon.com/images/I/41+wqZaBGEL._AC_US600_.jpg"/>
+    <hyperlink ref="L2" r:id="rId5" tooltip="https://www.amazon.co.uk/dp/B0FBTNXCD7"/>
+    <hyperlink ref="M2" r:id="rId6" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
+    <hyperlink ref="N2" r:id="rId7"/>
+    <hyperlink ref="C3" r:id="rId8" tooltip="https://www.amazon.co.uk/dp/B0DHL35LFT"/>
+    <hyperlink ref="G3" r:id="rId9" tooltip="https://www.amazon.co.uk/stores/JIMMY-UK/page/F8F01541-3149-48BD-8244-91EE9CFB1B04?lp_asin=B0DHL35LFT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J3" r:id="rId10" tooltip="https://www.amazon.co.uk/dp/B0DHL35LFT?psc=1"/>
+    <hyperlink ref="K3" r:id="rId11" tooltip="https://m.media-amazon.com/images/I/41H47yZFjXL._AC_US600_.jpg"/>
+    <hyperlink ref="L3" r:id="rId12" tooltip="https://www.amazon.co.uk/dp/B0DHL35LFT"/>
+    <hyperlink ref="M3" r:id="rId13" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
+    <hyperlink ref="N3" r:id="rId14"/>
+    <hyperlink ref="AW3" r:id="rId15" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ALIOQETPFAPZL"/>
+    <hyperlink ref="C4" r:id="rId16" tooltip="https://www.amazon.co.uk/dp/B0FN3GPQZM"/>
+    <hyperlink ref="G4" r:id="rId17" tooltip="https://www.amazon.co.uk/stores/ForSimpleLife/page/F3CD0189-4A3C-4A17-A156-96A66C79D903?lp_asin=B0FN3GPQZM&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J4" r:id="rId18" tooltip="https://www.amazon.co.uk/dp/B0FN3GPQZM?psc=1"/>
+    <hyperlink ref="K4" r:id="rId19" tooltip="https://images-na.ssl-images-amazon.com/images/I/71zFBwnc9GL._AC_US600_.jpg"/>
+    <hyperlink ref="L4" r:id="rId20" tooltip="https://www.amazon.co.uk/dp/B0GT4XL7VP"/>
+    <hyperlink ref="M4" r:id="rId21" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
+    <hyperlink ref="N4" r:id="rId22"/>
+    <hyperlink ref="AW4" r:id="rId23" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3EVTWEH1TBVG5"/>
+    <hyperlink ref="C5" r:id="rId24" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ"/>
+    <hyperlink ref="G5" r:id="rId25" tooltip="https://www.amazon.co.uk/stores/K%C3%A4rcherUK/page/F6053778-BFEE-41CB-9B1B-A16ECF7857D7?lp_asin=B0FPQMRBYZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J5" r:id="rId26" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ?psc=1"/>
+    <hyperlink ref="K5" r:id="rId27" tooltip="https://images-na.ssl-images-amazon.com/images/I/81MMJHIRoeL._AC_US600_.jpg"/>
+    <hyperlink ref="L5" r:id="rId28" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ"/>
+    <hyperlink ref="M5" r:id="rId29" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
+    <hyperlink ref="N5" r:id="rId30"/>
+    <hyperlink ref="AW5" r:id="rId31" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A36NXA8Q9KKCPB"/>
+    <hyperlink ref="C6" r:id="rId32" tooltip="https://www.amazon.co.uk/dp/B0DTS8VCFB"/>
+    <hyperlink ref="G6" r:id="rId33" tooltip="https://www.amazon.co.uk/stores/HAUSHOF/page/127A78F6-40A3-43F5-9B80-D084EFBE3029?lp_asin=B0DTS8VCFB&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J6" r:id="rId34" tooltip="https://www.amazon.co.uk/dp/B0DTS8VCFB?psc=1"/>
+    <hyperlink ref="K6" r:id="rId35" tooltip="https://m.media-amazon.com/images/I/41r3fkBQX2L._AC_US200_.jpg"/>
+    <hyperlink ref="L6" r:id="rId36" tooltip="https://www.amazon.co.uk/dp/B0DTS8VCFB"/>
+    <hyperlink ref="M6" r:id="rId37" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
+    <hyperlink ref="N6" r:id="rId38"/>
+    <hyperlink ref="C7" r:id="rId39" tooltip="https://www.amazon.co.uk/dp/B0DSCSR4MB"/>
+    <hyperlink ref="G7" r:id="rId40" tooltip="https://www.amazon.co.uk/stores/HAUSHOF/page/127A78F6-40A3-43F5-9B80-D084EFBE3029?lp_asin=B0DSCSR4MB&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J7" r:id="rId41" tooltip="https://www.amazon.co.uk/dp/B0DSCSR4MB?psc=1"/>
+    <hyperlink ref="K7" r:id="rId42" tooltip="https://m.media-amazon.com/images/I/418QfGErb0L._AC_US200_.jpg"/>
+    <hyperlink ref="L7" r:id="rId43" tooltip="https://www.amazon.co.uk/dp/B0DSCSR4MB"/>
+    <hyperlink ref="M7" r:id="rId44" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
+    <hyperlink ref="N7" r:id="rId45"/>
+    <hyperlink ref="C8" r:id="rId46" tooltip="https://www.amazon.co.uk/dp/B0GJDH8XTW"/>
+    <hyperlink ref="G8" r:id="rId47" tooltip="https://www.amazon.co.uk/stores/RANVOO/page/4598C590-4586-4B0D-914B-C8811A359BA2?lp_asin=B0GJDH8XTW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J8" r:id="rId48" tooltip="https://www.amazon.co.uk/dp/B0GJDH8XTW?psc=1"/>
+    <hyperlink ref="K8" r:id="rId49" tooltip="https://m.media-amazon.com/images/I/41-S5G-ONwL._AC_US200_.jpg"/>
+    <hyperlink ref="L8" r:id="rId50" tooltip="https://www.amazon.co.uk/dp/B0FX2VM7HM"/>
+    <hyperlink ref="M8" r:id="rId51" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
+    <hyperlink ref="N8" r:id="rId52"/>
+    <hyperlink ref="C9" r:id="rId53" tooltip="https://www.amazon.co.uk/dp/B0D7HF8S2W"/>
+    <hyperlink ref="G9" r:id="rId54" tooltip="https://www.amazon.co.uk/stores/Minthouz/page/10C1A6E0-EA82-42DE-BB39-8D8D80A76300?lp_asin=B0D7HF8S2W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J9" r:id="rId55" tooltip="https://www.amazon.co.uk/dp/B0D7HF8S2W?psc=1"/>
+    <hyperlink ref="K9" r:id="rId56" tooltip="https://m.media-amazon.com/images/I/31O99tSwr1L._AC_US200_.jpg"/>
+    <hyperlink ref="L9" r:id="rId57" tooltip="https://www.amazon.co.uk/dp/B0H8S6713Z"/>
+    <hyperlink ref="M9" r:id="rId58" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
+    <hyperlink ref="N9" r:id="rId59"/>
+    <hyperlink ref="C10" r:id="rId60" tooltip="https://www.amazon.co.uk/dp/B0F13NCPTZ"/>
+    <hyperlink ref="G10" r:id="rId61" tooltip="https://www.amazon.co.uk/Bear/b/ref=bl_dp_s_web_89011654031?ie=UTF8&amp;node=89011654031&amp;field-lbr_brands_browse-bin=Bear"/>
+    <hyperlink ref="J10" r:id="rId62" tooltip="https://www.amazon.co.uk/dp/B0F13NCPTZ?psc=1"/>
+    <hyperlink ref="K10" r:id="rId63" tooltip="https://images-na.ssl-images-amazon.com/images/I/612vIVIFq3L._AC_US600_.jpg"/>
+    <hyperlink ref="L10" r:id="rId64" tooltip="https://www.amazon.co.uk/dp/B0FGXMYDNH"/>
+    <hyperlink ref="M10" r:id="rId65" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
+    <hyperlink ref="N10" r:id="rId66"/>
+    <hyperlink ref="AW10" r:id="rId67" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2F3NLKIQATJ4E"/>
+    <hyperlink ref="C11" r:id="rId68" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7"/>
+    <hyperlink ref="G11" r:id="rId69" tooltip="https://www.amazon.co.uk/stores/TJEANLifeCleanCookBette/page/D57A3099-B34A-4AE2-BEED-A573440938CE?lp_asin=B0DSFM31F7&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J11" r:id="rId70" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7?psc=1"/>
+    <hyperlink ref="K11" r:id="rId71" tooltip="https://images-na.ssl-images-amazon.com/images/I/71k7WLBBcwL._AC_US600_.jpg"/>
+    <hyperlink ref="L11" r:id="rId72" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7"/>
+    <hyperlink ref="M11" r:id="rId73" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
+    <hyperlink ref="N11" r:id="rId74"/>
+    <hyperlink ref="AW11" r:id="rId75" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A21G0QWAFKJ6UP"/>
+    <hyperlink ref="C12" r:id="rId76" tooltip="https://www.amazon.co.uk/dp/B0CHMPZVZT"/>
+    <hyperlink ref="G12" r:id="rId77" tooltip="https://www.amazon.co.uk/JIGOO/b/ref=bl_dp_s_web_94911024031?ie=UTF8&amp;node=94911024031&amp;field-lbr_brands_browse-bin=JIGOO"/>
+    <hyperlink ref="J12" r:id="rId78" tooltip="https://www.amazon.co.uk/dp/B0CHMPZVZT?psc=1"/>
+    <hyperlink ref="K12" r:id="rId79" tooltip="https://m.media-amazon.com/images/I/51Y-O7KBSlL._AC_US200_.jpg"/>
+    <hyperlink ref="L12" r:id="rId80" tooltip="https://www.amazon.co.uk/dp/B0CHMPZVZT"/>
+    <hyperlink ref="M12" r:id="rId81" tooltip="https://www.amazon.co.uk/b?node=3147731"/>
+    <hyperlink ref="N12" r:id="rId82"/>
+    <hyperlink ref="C13" r:id="rId83" tooltip="https://www.amazon.co.uk/dp/B0D1QQXH6V"/>
+    <hyperlink ref="G13" r:id="rId84" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Amzany"/>
+    <hyperlink ref="J13" r:id="rId85" tooltip="https://www.amazon.co.uk/dp/B0D1QQXH6V?psc=1"/>
+    <hyperlink ref="K13" r:id="rId86" tooltip="https://images-na.ssl-images-amazon.com/images/I/71PNQ3QEyHL._AC_US600_.jpg"/>
+    <hyperlink ref="L13" r:id="rId87" tooltip="https://www.amazon.co.uk/dp/B0DBRWGZVR"/>
+    <hyperlink ref="M13" r:id="rId88" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
+    <hyperlink ref="N13" r:id="rId89"/>
+    <hyperlink ref="C14" r:id="rId90" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK"/>
+    <hyperlink ref="G14" r:id="rId91" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Gxzsk"/>
+    <hyperlink ref="J14" r:id="rId92" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK?psc=1"/>
+    <hyperlink ref="K14" r:id="rId93" tooltip="https://m.media-amazon.com/images/I/51vT9VPsfxL._AC_US200_.jpg"/>
+    <hyperlink ref="L14" r:id="rId94" tooltip="https://www.amazon.co.uk/dp/B0FFZWJTL1"/>
+    <hyperlink ref="M14" r:id="rId95" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
+    <hyperlink ref="N14" r:id="rId96"/>
+    <hyperlink ref="C15" r:id="rId97" tooltip="https://www.amazon.co.uk/dp/B0D5WTVR91"/>
+    <hyperlink ref="G15" r:id="rId98" tooltip="https://www.amazon.co.uk/stores/Convenienceforyourhome/page/818AA347-F8E9-4151-B8B2-A1E50E5C29AE?lp_asin=B0D5WTVR91&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J15" r:id="rId99" tooltip="https://www.amazon.co.uk/dp/B0D5WTVR91?psc=1"/>
+    <hyperlink ref="K15" r:id="rId100" tooltip="https://m.media-amazon.com/images/I/31W1ZXCx81L._AC_US200_.jpg"/>
+    <hyperlink ref="L15" r:id="rId101" tooltip="https://www.amazon.co.uk/dp/B0D5WTH79H"/>
+    <hyperlink ref="M15" r:id="rId102" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
+    <hyperlink ref="N15" r:id="rId103"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <drawing r:id="rId71"/>
+  <drawing r:id="rId104"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -4167,38 +5187,314 @@
         <v>21</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>129</v>
+        <v>302</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>130</v>
+        <v>303</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>131</v>
+        <v>304</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>132</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="B2" s="15">
-        <v>0</v>
+        <v>658</v>
       </c>
       <c r="C2" s="15">
-        <v>0</v>
+        <v>48804</v>
       </c>
       <c r="D2" s="15">
-        <v>0</v>
+        <v>9440</v>
       </c>
       <c r="E2" s="15">
-        <v>0</v>
-      </c>
-      <c r="F2" s="19">
-        <v>6.69</v>
+        <v>700165</v>
+      </c>
+      <c r="F2" s="20">
+        <v>74.17</v>
       </c>
       <c r="G2" s="22">
+        <v>0.8084</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="15">
+        <v>90</v>
+      </c>
+      <c r="C3" s="15">
+        <v>17999</v>
+      </c>
+      <c r="D3" s="15">
+        <v>1376</v>
+      </c>
+      <c r="E3" s="15">
+        <v>275186</v>
+      </c>
+      <c r="F3" s="20">
+        <v>199.99</v>
+      </c>
+      <c r="G3" s="22">
+        <v>0.1106</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B4" s="15">
+        <v>60</v>
+      </c>
+      <c r="C4" s="15">
+        <v>5999</v>
+      </c>
+      <c r="D4" s="15">
+        <v>477</v>
+      </c>
+      <c r="E4" s="15">
+        <v>47695</v>
+      </c>
+      <c r="F4" s="20">
+        <v>99.99</v>
+      </c>
+      <c r="G4" s="22">
+        <v>0.0737</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="B5" s="15">
+        <v>6</v>
+      </c>
+      <c r="C5" s="15">
+        <v>270</v>
+      </c>
+      <c r="D5" s="15">
+        <v>1144</v>
+      </c>
+      <c r="E5" s="15">
+        <v>51469</v>
+      </c>
+      <c r="F5" s="20">
+        <v>44.99</v>
+      </c>
+      <c r="G5" s="22">
+        <v>0.0074</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="B6" s="15">
+        <v>0</v>
+      </c>
+      <c r="C6" s="15">
+        <v>0</v>
+      </c>
+      <c r="D6" s="15">
+        <v>25</v>
+      </c>
+      <c r="E6" s="15">
+        <v>3574</v>
+      </c>
+      <c r="F6" s="20">
+        <v>142.98</v>
+      </c>
+      <c r="G6" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7" s="15">
+        <v>0</v>
+      </c>
+      <c r="C7" s="15">
+        <v>0</v>
+      </c>
+      <c r="D7" s="15">
+        <v>0</v>
+      </c>
+      <c r="E7" s="15">
+        <v>0</v>
+      </c>
+      <c r="F7" s="20">
+        <v>0</v>
+      </c>
+      <c r="G7" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="B8" s="15">
+        <v>0</v>
+      </c>
+      <c r="C8" s="15">
+        <v>0</v>
+      </c>
+      <c r="D8" s="15">
+        <v>0</v>
+      </c>
+      <c r="E8" s="15">
+        <v>0</v>
+      </c>
+      <c r="F8" s="20">
+        <v>0</v>
+      </c>
+      <c r="G8" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="B9" s="15">
+        <v>0</v>
+      </c>
+      <c r="C9" s="15">
+        <v>0</v>
+      </c>
+      <c r="D9" s="15">
+        <v>0</v>
+      </c>
+      <c r="E9" s="15">
+        <v>0</v>
+      </c>
+      <c r="F9" s="20">
+        <v>19.52</v>
+      </c>
+      <c r="G9" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="B10" s="15">
+        <v>0</v>
+      </c>
+      <c r="C10" s="15">
+        <v>0</v>
+      </c>
+      <c r="D10" s="15">
+        <v>121</v>
+      </c>
+      <c r="E10" s="15">
+        <v>5663</v>
+      </c>
+      <c r="F10" s="20">
+        <v>46.8</v>
+      </c>
+      <c r="G10" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="B11" s="15">
+        <v>0</v>
+      </c>
+      <c r="C11" s="15">
+        <v>0</v>
+      </c>
+      <c r="D11" s="15">
+        <v>0</v>
+      </c>
+      <c r="E11" s="15">
+        <v>0</v>
+      </c>
+      <c r="F11" s="20">
+        <v>0</v>
+      </c>
+      <c r="G11" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="B12" s="15">
+        <v>0</v>
+      </c>
+      <c r="C12" s="15">
+        <v>0</v>
+      </c>
+      <c r="D12" s="15">
+        <v>2</v>
+      </c>
+      <c r="E12" s="15">
+        <v>183</v>
+      </c>
+      <c r="F12" s="20">
+        <v>91.74</v>
+      </c>
+      <c r="G12" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="B13" s="15">
+        <v>0</v>
+      </c>
+      <c r="C13" s="15">
+        <v>0</v>
+      </c>
+      <c r="D13" s="15">
+        <v>0</v>
+      </c>
+      <c r="E13" s="15">
+        <v>0</v>
+      </c>
+      <c r="F13" s="20">
+        <v>0</v>
+      </c>
+      <c r="G13" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="B14" s="15">
+        <v>0</v>
+      </c>
+      <c r="C14" s="15">
+        <v>0</v>
+      </c>
+      <c r="D14" s="15">
+        <v>0</v>
+      </c>
+      <c r="E14" s="15">
+        <v>0</v>
+      </c>
+      <c r="F14" s="20">
+        <v>0</v>
+      </c>
+      <c r="G14" s="22">
         <v>0</v>
       </c>
     </row>
@@ -4210,7 +5506,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -4221,7 +5517,7 @@
   <sheetData>
     <row r="1" ht="27" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>134</v>
+        <v>306</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>19</v>
@@ -4230,38 +5526,199 @@
         <v>21</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>129</v>
+        <v>302</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>130</v>
+        <v>303</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>131</v>
+        <v>304</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>132</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="B2" s="15">
-        <v>0</v>
+        <v>658</v>
       </c>
       <c r="C2" s="15">
-        <v>0</v>
+        <v>30824</v>
       </c>
       <c r="D2" s="15">
-        <v>0</v>
+        <v>9440</v>
       </c>
       <c r="E2" s="15">
-        <v>0</v>
-      </c>
-      <c r="F2" s="19">
-        <v>6.69</v>
+        <v>442217</v>
+      </c>
+      <c r="F2" s="20">
+        <v>46.85</v>
       </c>
       <c r="G2" s="22">
+        <v>0.8084</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="15">
+        <v>90</v>
+      </c>
+      <c r="C3" s="15">
+        <v>17999</v>
+      </c>
+      <c r="D3" s="15">
+        <v>1376</v>
+      </c>
+      <c r="E3" s="15">
+        <v>275186</v>
+      </c>
+      <c r="F3" s="20">
+        <v>199.99</v>
+      </c>
+      <c r="G3" s="22">
+        <v>0.1106</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B4" s="15">
+        <v>60</v>
+      </c>
+      <c r="C4" s="15">
+        <v>5999</v>
+      </c>
+      <c r="D4" s="15">
+        <v>477</v>
+      </c>
+      <c r="E4" s="15">
+        <v>47695</v>
+      </c>
+      <c r="F4" s="20">
+        <v>99.99</v>
+      </c>
+      <c r="G4" s="22">
+        <v>0.0737</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="B5" s="15">
+        <v>6</v>
+      </c>
+      <c r="C5" s="15">
+        <v>270</v>
+      </c>
+      <c r="D5" s="15">
+        <v>1144</v>
+      </c>
+      <c r="E5" s="15">
+        <v>51469</v>
+      </c>
+      <c r="F5" s="20">
+        <v>44.99</v>
+      </c>
+      <c r="G5" s="22">
+        <v>0.0074</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="B6" s="15">
+        <v>0</v>
+      </c>
+      <c r="C6" s="15">
+        <v>0</v>
+      </c>
+      <c r="D6" s="15">
+        <v>25</v>
+      </c>
+      <c r="E6" s="15">
+        <v>3574</v>
+      </c>
+      <c r="F6" s="20">
+        <v>142.98</v>
+      </c>
+      <c r="G6" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="B7" s="15">
+        <v>0</v>
+      </c>
+      <c r="C7" s="15">
+        <v>0</v>
+      </c>
+      <c r="D7" s="15">
+        <v>0</v>
+      </c>
+      <c r="E7" s="15">
+        <v>0</v>
+      </c>
+      <c r="F7" s="20">
+        <v>0</v>
+      </c>
+      <c r="G7" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="B8" s="15">
+        <v>0</v>
+      </c>
+      <c r="C8" s="15">
+        <v>0</v>
+      </c>
+      <c r="D8" s="15">
+        <v>121</v>
+      </c>
+      <c r="E8" s="15">
+        <v>5663</v>
+      </c>
+      <c r="F8" s="20">
+        <v>46.8</v>
+      </c>
+      <c r="G8" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="B9" s="15">
+        <v>0</v>
+      </c>
+      <c r="C9" s="15">
+        <v>0</v>
+      </c>
+      <c r="D9" s="15">
+        <v>2</v>
+      </c>
+      <c r="E9" s="15">
+        <v>183</v>
+      </c>
+      <c r="F9" s="20">
+        <v>91.74</v>
+      </c>
+      <c r="G9" s="22">
         <v>0</v>
       </c>
     </row>
@@ -4281,37 +5738,37 @@
   <sheetData>
     <row r="1" ht="45" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>136</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
-        <v>137</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3" ht="200" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="32" t="s">
-        <v>138</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
-        <v>139</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="32" t="s">
-        <v>140</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1" spans="1:1" s="33" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="34" t="s">
-        <v>141</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
-        <v>142</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
